--- a/research/traditional_assets/database/data/singapore/singapore_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_coal_related_energy.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09273596451495866</v>
+        <v>0.09261566337528325</v>
       </c>
       <c r="C2">
-        <v>512.3313632304213</v>
+        <v>507.7603552500836</v>
       </c>
       <c r="D2">
-        <v>426.6313632304213</v>
+        <v>427.4203552500836</v>
       </c>
       <c r="E2">
-        <v>-233</v>
+        <v>-227.64</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="G2">
         <v>85.7</v>
@@ -1445,28 +1445,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.269608</v>
       </c>
       <c r="N2">
-        <v>47.16666666666667</v>
+        <v>46.89705866666667</v>
       </c>
       <c r="O2">
-        <v>8.018333333333334</v>
+        <v>7.972499973333335</v>
       </c>
       <c r="P2">
-        <v>39.14833333333334</v>
+        <v>38.92455869333334</v>
       </c>
       <c r="Q2">
-        <v>50.24833333333334</v>
+        <v>50.02455869333334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09273596451495866</v>
+        <v>0.09312946805584166</v>
       </c>
       <c r="T2">
-        <v>1.083971466858168</v>
+        <v>1.093059308448999</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>174.9453527590675</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09261566337528325</v>
+        <v>0.09249536223560781</v>
       </c>
       <c r="C3">
-        <v>507.7603552500836</v>
+        <v>503.1922709262404</v>
       </c>
       <c r="D3">
-        <v>427.4203552500836</v>
+        <v>428.2122709262405</v>
       </c>
       <c r="E3">
-        <v>-227.64</v>
+        <v>-222.28</v>
       </c>
       <c r="F3">
-        <v>5.36</v>
+        <v>10.72</v>
       </c>
       <c r="G3">
         <v>85.7</v>
@@ -1527,28 +1527,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M3">
-        <v>0.269608</v>
+        <v>0.539216</v>
       </c>
       <c r="N3">
-        <v>46.89705866666667</v>
+        <v>46.62745066666667</v>
       </c>
       <c r="O3">
-        <v>7.972499973333335</v>
+        <v>7.926666613333334</v>
       </c>
       <c r="P3">
-        <v>38.92455869333334</v>
+        <v>38.70078405333334</v>
       </c>
       <c r="Q3">
-        <v>50.02455869333334</v>
+        <v>49.80078405333334</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09312946805584166</v>
+        <v>0.09353100228123246</v>
       </c>
       <c r="T3">
-        <v>1.093059308448999</v>
+        <v>1.102332616194745</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>174.9453527590675</v>
+        <v>87.47267637953374</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09249536223560781</v>
+        <v>0.09237506109593238</v>
       </c>
       <c r="C4">
-        <v>503.1922709262404</v>
+        <v>498.6271265397291</v>
       </c>
       <c r="D4">
-        <v>428.2122709262405</v>
+        <v>429.0071265397291</v>
       </c>
       <c r="E4">
-        <v>-222.28</v>
+        <v>-216.92</v>
       </c>
       <c r="F4">
-        <v>10.72</v>
+        <v>16.08</v>
       </c>
       <c r="G4">
         <v>85.7</v>
@@ -1609,28 +1609,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M4">
-        <v>0.539216</v>
+        <v>0.8088239999999999</v>
       </c>
       <c r="N4">
-        <v>46.62745066666667</v>
+        <v>46.35784266666667</v>
       </c>
       <c r="O4">
-        <v>7.926666613333334</v>
+        <v>7.880833253333335</v>
       </c>
       <c r="P4">
-        <v>38.70078405333334</v>
+        <v>38.47700941333333</v>
       </c>
       <c r="Q4">
-        <v>49.80078405333334</v>
+        <v>49.57700941333334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09353100228123246</v>
+        <v>0.09394081556281689</v>
       </c>
       <c r="T4">
-        <v>1.102332616194745</v>
+        <v>1.111797126162053</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>87.47267637953374</v>
+        <v>58.31511758635584</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09237506109593238</v>
+        <v>0.09225475995625695</v>
       </c>
       <c r="C5">
-        <v>498.6271265397291</v>
+        <v>494.0649384924947</v>
       </c>
       <c r="D5">
-        <v>429.0071265397291</v>
+        <v>429.8049384924947</v>
       </c>
       <c r="E5">
-        <v>-216.92</v>
+        <v>-211.56</v>
       </c>
       <c r="F5">
-        <v>16.08</v>
+        <v>21.44</v>
       </c>
       <c r="G5">
         <v>85.7</v>
@@ -1691,28 +1691,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M5">
-        <v>0.8088239999999999</v>
+        <v>1.078432</v>
       </c>
       <c r="N5">
-        <v>46.35784266666667</v>
+        <v>46.08823466666667</v>
       </c>
       <c r="O5">
-        <v>7.880833253333335</v>
+        <v>7.834999893333335</v>
       </c>
       <c r="P5">
-        <v>38.47700941333333</v>
+        <v>38.25323477333334</v>
       </c>
       <c r="Q5">
-        <v>49.57700941333334</v>
+        <v>49.35323477333334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09394081556281689</v>
+        <v>0.094359166621101</v>
       </c>
       <c r="T5">
-        <v>1.111797126162053</v>
+        <v>1.121458813420346</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>58.31511758635584</v>
+        <v>43.73633818976688</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09225475995625695</v>
+        <v>0.09213445881658151</v>
       </c>
       <c r="C6">
-        <v>494.0649384924947</v>
+        <v>489.5057233087189</v>
       </c>
       <c r="D6">
-        <v>429.8049384924947</v>
+        <v>430.605723308719</v>
       </c>
       <c r="E6">
-        <v>-211.56</v>
+        <v>-206.2</v>
       </c>
       <c r="F6">
-        <v>21.44</v>
+        <v>26.8</v>
       </c>
       <c r="G6">
         <v>85.7</v>
@@ -1773,28 +1773,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M6">
-        <v>1.078432</v>
+        <v>1.34804</v>
       </c>
       <c r="N6">
-        <v>46.08823466666667</v>
+        <v>45.81862666666667</v>
       </c>
       <c r="O6">
-        <v>7.834999893333335</v>
+        <v>7.789166533333336</v>
       </c>
       <c r="P6">
-        <v>38.25323477333334</v>
+        <v>38.02946013333334</v>
       </c>
       <c r="Q6">
-        <v>49.35323477333334</v>
+        <v>49.12946013333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.094359166621101</v>
+        <v>0.0947863250700858</v>
       </c>
       <c r="T6">
-        <v>1.121458813420346</v>
+        <v>1.13132390462092</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.73633818976688</v>
+        <v>34.98907055181351</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09213445881658151</v>
+        <v>0.09201415767690609</v>
       </c>
       <c r="C7">
-        <v>489.5057233087189</v>
+        <v>484.9494976359602</v>
       </c>
       <c r="D7">
-        <v>430.605723308719</v>
+        <v>431.4094976359602</v>
       </c>
       <c r="E7">
-        <v>-206.2</v>
+        <v>-200.84</v>
       </c>
       <c r="F7">
-        <v>26.8</v>
+        <v>32.16</v>
       </c>
       <c r="G7">
         <v>85.7</v>
@@ -1855,28 +1855,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M7">
-        <v>1.34804</v>
+        <v>1.617648</v>
       </c>
       <c r="N7">
-        <v>45.81862666666667</v>
+        <v>45.54901866666667</v>
       </c>
       <c r="O7">
-        <v>7.789166533333336</v>
+        <v>7.743333173333334</v>
       </c>
       <c r="P7">
-        <v>38.02946013333334</v>
+        <v>37.80568549333334</v>
       </c>
       <c r="Q7">
-        <v>49.12946013333334</v>
+        <v>48.90568549333334</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0947863250700858</v>
+        <v>0.09522257199670861</v>
       </c>
       <c r="T7">
-        <v>1.13132390462092</v>
+        <v>1.141398891378952</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.98907055181351</v>
+        <v>29.15755879317791</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09201415767690609</v>
+        <v>0.09189385653723067</v>
       </c>
       <c r="C8">
-        <v>484.9494976359603</v>
+        <v>480.3962782463077</v>
       </c>
       <c r="D8">
-        <v>431.4094976359602</v>
+        <v>432.2162782463076</v>
       </c>
       <c r="E8">
-        <v>-200.84</v>
+        <v>-195.48</v>
       </c>
       <c r="F8">
-        <v>32.16</v>
+        <v>37.52</v>
       </c>
       <c r="G8">
         <v>85.7</v>
@@ -1937,28 +1937,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M8">
-        <v>1.617648</v>
+        <v>1.887256</v>
       </c>
       <c r="N8">
-        <v>45.54901866666667</v>
+        <v>45.27941066666667</v>
       </c>
       <c r="O8">
-        <v>7.743333173333334</v>
+        <v>7.697499813333335</v>
       </c>
       <c r="P8">
-        <v>37.80568549333334</v>
+        <v>37.58191085333333</v>
       </c>
       <c r="Q8">
-        <v>48.90568549333334</v>
+        <v>48.68191085333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09522257199670861</v>
+        <v>0.09566820057766738</v>
       </c>
       <c r="T8">
-        <v>1.141398891378952</v>
+        <v>1.151690544518877</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.15755879317792</v>
+        <v>24.99219325129536</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09189385653723066</v>
+        <v>0.09177355539755523</v>
       </c>
       <c r="C9">
-        <v>480.3962782463078</v>
+        <v>475.8460820375481</v>
       </c>
       <c r="D9">
-        <v>432.2162782463078</v>
+        <v>433.026082037548</v>
       </c>
       <c r="E9">
-        <v>-195.48</v>
+        <v>-190.12</v>
       </c>
       <c r="F9">
-        <v>37.52</v>
+        <v>42.88</v>
       </c>
       <c r="G9">
         <v>85.7</v>
@@ -2019,28 +2019,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M9">
-        <v>1.887256</v>
+        <v>2.156864</v>
       </c>
       <c r="N9">
-        <v>45.27941066666667</v>
+        <v>45.00980266666667</v>
       </c>
       <c r="O9">
-        <v>7.697499813333335</v>
+        <v>7.651666453333335</v>
       </c>
       <c r="P9">
-        <v>37.58191085333333</v>
+        <v>37.35813621333334</v>
       </c>
       <c r="Q9">
-        <v>48.68191085333333</v>
+        <v>48.45813621333334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09566820057766738</v>
+        <v>0.09612351673647308</v>
       </c>
       <c r="T9">
-        <v>1.151690544518877</v>
+        <v>1.162205929248801</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.99219325129536</v>
+        <v>21.86816909488344</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09177355539755523</v>
+        <v>0.09165325425787982</v>
       </c>
       <c r="C10">
-        <v>475.8460820375481</v>
+        <v>471.2989260343443</v>
       </c>
       <c r="D10">
-        <v>433.026082037548</v>
+        <v>433.8389260343443</v>
       </c>
       <c r="E10">
-        <v>-190.12</v>
+        <v>-184.76</v>
       </c>
       <c r="F10">
-        <v>42.88</v>
+        <v>48.23999999999999</v>
       </c>
       <c r="G10">
         <v>85.7</v>
@@ -2101,28 +2101,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M10">
-        <v>2.156864</v>
+        <v>2.426472</v>
       </c>
       <c r="N10">
-        <v>45.00980266666667</v>
+        <v>44.74019466666667</v>
       </c>
       <c r="O10">
-        <v>7.651666453333335</v>
+        <v>7.605833093333335</v>
       </c>
       <c r="P10">
-        <v>37.35813621333334</v>
+        <v>37.13436157333334</v>
       </c>
       <c r="Q10">
-        <v>48.45813621333334</v>
+        <v>48.23436157333334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09612351673647308</v>
+        <v>0.09658883984382396</v>
       </c>
       <c r="T10">
-        <v>1.162205929248801</v>
+        <v>1.172952421335427</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.86816909488344</v>
+        <v>19.43837252878528</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09165325425787982</v>
+        <v>0.09153295311820436</v>
       </c>
       <c r="C11">
-        <v>471.2989260343443</v>
+        <v>466.7548273894307</v>
       </c>
       <c r="D11">
-        <v>433.8389260343443</v>
+        <v>434.6548273894307</v>
       </c>
       <c r="E11">
-        <v>-184.76</v>
+        <v>-179.4</v>
       </c>
       <c r="F11">
-        <v>48.23999999999999</v>
+        <v>53.59999999999999</v>
       </c>
       <c r="G11">
         <v>85.7</v>
@@ -2183,28 +2183,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M11">
-        <v>2.426472</v>
+        <v>2.696079999999999</v>
       </c>
       <c r="N11">
-        <v>44.74019466666667</v>
+        <v>44.47058666666667</v>
       </c>
       <c r="O11">
-        <v>7.605833093333335</v>
+        <v>7.559999733333334</v>
       </c>
       <c r="P11">
-        <v>37.13436157333334</v>
+        <v>36.91058693333333</v>
       </c>
       <c r="Q11">
-        <v>48.23436157333334</v>
+        <v>48.01058693333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09658883984382396</v>
+        <v>0.09706450346467152</v>
       </c>
       <c r="T11">
-        <v>1.172952421335427</v>
+        <v>1.18393772435731</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.43837252878528</v>
+        <v>17.49453527590675</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09153295311820436</v>
+        <v>0.09141265197852895</v>
       </c>
       <c r="C12">
-        <v>466.7548273894307</v>
+        <v>462.2138033848167</v>
       </c>
       <c r="D12">
-        <v>434.6548273894307</v>
+        <v>435.4738033848167</v>
       </c>
       <c r="E12">
-        <v>-179.4</v>
+        <v>-174.04</v>
       </c>
       <c r="F12">
-        <v>53.6</v>
+        <v>58.96</v>
       </c>
       <c r="G12">
         <v>85.7</v>
@@ -2265,28 +2265,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M12">
-        <v>2.69608</v>
+        <v>2.965688</v>
       </c>
       <c r="N12">
-        <v>44.47058666666667</v>
+        <v>44.20097866666667</v>
       </c>
       <c r="O12">
-        <v>7.559999733333334</v>
+        <v>7.514166373333334</v>
       </c>
       <c r="P12">
-        <v>36.91058693333333</v>
+        <v>36.68681229333334</v>
       </c>
       <c r="Q12">
-        <v>48.01058693333334</v>
+        <v>47.78681229333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09706450346467152</v>
+        <v>0.0975508561556505</v>
       </c>
       <c r="T12">
-        <v>1.18393772435731</v>
+        <v>1.195169888121259</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.49453527590675</v>
+        <v>15.90412297809704</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09141265197852895</v>
+        <v>0.09129235083885351</v>
       </c>
       <c r="C13">
-        <v>462.2138033848167</v>
+        <v>457.6758714330097</v>
       </c>
       <c r="D13">
-        <v>435.4738033848167</v>
+        <v>436.2958714330097</v>
       </c>
       <c r="E13">
-        <v>-174.04</v>
+        <v>-168.68</v>
       </c>
       <c r="F13">
-        <v>58.96</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="G13">
         <v>85.7</v>
@@ -2347,28 +2347,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M13">
-        <v>2.965688</v>
+        <v>3.235296</v>
       </c>
       <c r="N13">
-        <v>44.20097866666667</v>
+        <v>43.93137066666667</v>
       </c>
       <c r="O13">
-        <v>7.514166373333334</v>
+        <v>7.468333013333335</v>
       </c>
       <c r="P13">
-        <v>36.68681229333334</v>
+        <v>36.46303765333334</v>
       </c>
       <c r="Q13">
-        <v>47.78681229333334</v>
+        <v>47.56303765333334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0975508561556505</v>
+        <v>0.09804826231687899</v>
       </c>
       <c r="T13">
-        <v>1.195169888121259</v>
+        <v>1.206657328334388</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.90412297809704</v>
+        <v>14.57877939658896</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09129235083885351</v>
+        <v>0.09117204969917808</v>
       </c>
       <c r="C14">
-        <v>457.6758714330097</v>
+        <v>453.1410490782475</v>
       </c>
       <c r="D14">
-        <v>436.2958714330097</v>
+        <v>437.1210490782475</v>
       </c>
       <c r="E14">
-        <v>-168.68</v>
+        <v>-163.32</v>
       </c>
       <c r="F14">
-        <v>64.31999999999999</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="G14">
         <v>85.7</v>
@@ -2429,28 +2429,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M14">
-        <v>3.235296</v>
+        <v>3.504904</v>
       </c>
       <c r="N14">
-        <v>43.93137066666667</v>
+        <v>43.66176266666667</v>
       </c>
       <c r="O14">
-        <v>7.468333013333335</v>
+        <v>7.422499653333334</v>
       </c>
       <c r="P14">
-        <v>36.46303765333334</v>
+        <v>36.23926301333334</v>
       </c>
       <c r="Q14">
-        <v>47.56303765333334</v>
+        <v>47.33926301333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09804826231687899</v>
+        <v>0.09855710310250354</v>
       </c>
       <c r="T14">
-        <v>1.206657328334388</v>
+        <v>1.218408847632876</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.57877939658896</v>
+        <v>13.45733482762058</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09117204969917808</v>
+        <v>0.09122604855950264</v>
       </c>
       <c r="C15">
-        <v>453.1410490782475</v>
+        <v>447.4102707126243</v>
       </c>
       <c r="D15">
-        <v>437.1210490782475</v>
+        <v>436.7502707126243</v>
       </c>
       <c r="E15">
-        <v>-163.32</v>
+        <v>-157.96</v>
       </c>
       <c r="F15">
-        <v>69.68000000000001</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="G15">
         <v>85.7</v>
@@ -2511,45 +2511,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M15">
-        <v>3.504904</v>
+        <v>3.887072</v>
       </c>
       <c r="N15">
-        <v>43.66176266666667</v>
+        <v>43.27959466666667</v>
       </c>
       <c r="O15">
-        <v>7.422499653333334</v>
+        <v>7.357531093333334</v>
       </c>
       <c r="P15">
-        <v>36.23926301333334</v>
+        <v>35.92206357333333</v>
       </c>
       <c r="Q15">
-        <v>47.33926301333334</v>
+        <v>47.02206357333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09855710310250354</v>
+        <v>0.09907777739477053</v>
       </c>
       <c r="T15">
-        <v>1.218408847632876</v>
+        <v>1.230433658077842</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.17</v>
       </c>
       <c r="W15">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.45733482762058</v>
+        <v>12.13424054575441</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09122604855950264</v>
+        <v>0.09111819741982723</v>
       </c>
       <c r="C16">
-        <v>447.4102707126243</v>
+        <v>442.7914484721749</v>
       </c>
       <c r="D16">
-        <v>436.7502707126243</v>
+        <v>437.4914484721749</v>
       </c>
       <c r="E16">
-        <v>-157.96</v>
+        <v>-152.6</v>
       </c>
       <c r="F16">
-        <v>75.04000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G16">
         <v>85.7</v>
@@ -2593,28 +2593,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M16">
-        <v>3.887072</v>
+        <v>4.16472</v>
       </c>
       <c r="N16">
-        <v>43.27959466666667</v>
+        <v>43.00194666666667</v>
       </c>
       <c r="O16">
-        <v>7.357531093333334</v>
+        <v>7.310330933333335</v>
       </c>
       <c r="P16">
-        <v>35.92206357333333</v>
+        <v>35.69161573333334</v>
       </c>
       <c r="Q16">
-        <v>47.02206357333333</v>
+        <v>46.79161573333334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09907777739477053</v>
+        <v>0.09961070284685557</v>
       </c>
       <c r="T16">
-        <v>1.230433658077842</v>
+        <v>1.242741405239159</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.13424054575441</v>
+        <v>11.32529117603745</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09111819741982723</v>
+        <v>0.0910103462801518</v>
       </c>
       <c r="C17">
-        <v>442.7914484721749</v>
+        <v>438.1751461079399</v>
       </c>
       <c r="D17">
-        <v>437.4914484721749</v>
+        <v>438.2351461079399</v>
       </c>
       <c r="E17">
-        <v>-152.6</v>
+        <v>-147.24</v>
       </c>
       <c r="F17">
-        <v>80.39999999999999</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="G17">
         <v>85.7</v>
@@ -2675,28 +2675,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M17">
-        <v>4.164719999999999</v>
+        <v>4.442368</v>
       </c>
       <c r="N17">
-        <v>43.00194666666667</v>
+        <v>42.72429866666667</v>
       </c>
       <c r="O17">
-        <v>7.310330933333335</v>
+        <v>7.263130773333335</v>
       </c>
       <c r="P17">
-        <v>35.69161573333334</v>
+        <v>35.46116789333333</v>
       </c>
       <c r="Q17">
-        <v>46.79161573333334</v>
+        <v>46.56116789333333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09961070284685557</v>
+        <v>0.1001563170001807</v>
       </c>
       <c r="T17">
-        <v>1.242741405239159</v>
+        <v>1.255342193999555</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.32529117603745</v>
+        <v>10.6174604775351</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0910103462801518</v>
+        <v>0.09090249514047637</v>
       </c>
       <c r="C18">
-        <v>438.1751461079399</v>
+        <v>433.5613764925164</v>
       </c>
       <c r="D18">
-        <v>438.2351461079399</v>
+        <v>438.9813764925163</v>
       </c>
       <c r="E18">
-        <v>-147.24</v>
+        <v>-141.88</v>
       </c>
       <c r="F18">
-        <v>85.76000000000001</v>
+        <v>91.12</v>
       </c>
       <c r="G18">
         <v>85.7</v>
@@ -2757,28 +2757,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M18">
-        <v>4.442368</v>
+        <v>4.720016</v>
       </c>
       <c r="N18">
-        <v>42.72429866666667</v>
+        <v>42.44665066666667</v>
       </c>
       <c r="O18">
-        <v>7.263130773333335</v>
+        <v>7.215930613333335</v>
       </c>
       <c r="P18">
-        <v>35.46116789333333</v>
+        <v>35.23072005333334</v>
       </c>
       <c r="Q18">
-        <v>46.56116789333333</v>
+        <v>46.33072005333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1001563170001807</v>
+        <v>0.1007150784825016</v>
       </c>
       <c r="T18">
-        <v>1.255342193999555</v>
+        <v>1.268246616224057</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.6174604775351</v>
+        <v>9.992903978856569</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09090249514047637</v>
+        <v>0.09104862400080092</v>
       </c>
       <c r="C19">
-        <v>433.5613764925164</v>
+        <v>427.190909231272</v>
       </c>
       <c r="D19">
-        <v>438.9813764925163</v>
+        <v>437.970909231272</v>
       </c>
       <c r="E19">
-        <v>-141.88</v>
+        <v>-136.52</v>
       </c>
       <c r="F19">
-        <v>91.12</v>
+        <v>96.48000000000002</v>
       </c>
       <c r="G19">
         <v>85.7</v>
@@ -2839,45 +2839,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M19">
-        <v>4.720016</v>
+        <v>5.16168</v>
       </c>
       <c r="N19">
-        <v>42.44665066666667</v>
+        <v>42.00498666666667</v>
       </c>
       <c r="O19">
-        <v>7.215930613333335</v>
+        <v>7.140847733333334</v>
       </c>
       <c r="P19">
-        <v>35.23072005333334</v>
+        <v>34.86413893333334</v>
       </c>
       <c r="Q19">
-        <v>46.33072005333334</v>
+        <v>45.96413893333334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1007150784825016</v>
+        <v>0.1012874682936597</v>
       </c>
       <c r="T19">
-        <v>1.268246616224057</v>
+        <v>1.281465780454034</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.17</v>
       </c>
       <c r="W19">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.992903978856569</v>
+        <v>9.137851758858872</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09104862400080094</v>
+        <v>0.09095488286112551</v>
       </c>
       <c r="C20">
-        <v>427.1909092312719</v>
+        <v>422.4785846466948</v>
       </c>
       <c r="D20">
-        <v>437.9709092312719</v>
+        <v>438.6185846466948</v>
       </c>
       <c r="E20">
-        <v>-136.52</v>
+        <v>-131.16</v>
       </c>
       <c r="F20">
-        <v>96.47999999999999</v>
+        <v>101.84</v>
       </c>
       <c r="G20">
         <v>85.7</v>
@@ -2921,28 +2921,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M20">
-        <v>5.16168</v>
+        <v>5.44844</v>
       </c>
       <c r="N20">
-        <v>42.00498666666667</v>
+        <v>41.71822666666667</v>
       </c>
       <c r="O20">
-        <v>7.140847733333335</v>
+        <v>7.092098533333335</v>
       </c>
       <c r="P20">
-        <v>34.86413893333334</v>
+        <v>34.62612813333334</v>
       </c>
       <c r="Q20">
-        <v>45.96413893333334</v>
+        <v>45.72612813333334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1012874682936597</v>
+        <v>0.1018739911865747</v>
       </c>
       <c r="T20">
-        <v>1.281465780454034</v>
+        <v>1.295011343800802</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.137851758858876</v>
+        <v>8.656912192603144</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09095488286112551</v>
+        <v>0.09086114172145009</v>
       </c>
       <c r="C21">
-        <v>422.4785846466948</v>
+        <v>417.7681784758279</v>
       </c>
       <c r="D21">
-        <v>438.6185846466948</v>
+        <v>439.2681784758279</v>
       </c>
       <c r="E21">
-        <v>-131.16</v>
+        <v>-125.8</v>
       </c>
       <c r="F21">
-        <v>101.84</v>
+        <v>107.2</v>
       </c>
       <c r="G21">
         <v>85.7</v>
@@ -3003,28 +3003,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M21">
-        <v>5.44844</v>
+        <v>5.7352</v>
       </c>
       <c r="N21">
-        <v>41.71822666666667</v>
+        <v>41.43146666666667</v>
       </c>
       <c r="O21">
-        <v>7.092098533333335</v>
+        <v>7.043349333333335</v>
       </c>
       <c r="P21">
-        <v>34.62612813333334</v>
+        <v>34.38811733333334</v>
       </c>
       <c r="Q21">
-        <v>45.72612813333334</v>
+        <v>45.48811733333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1018739911865747</v>
+        <v>0.1024751771518126</v>
       </c>
       <c r="T21">
-        <v>1.295011343800802</v>
+        <v>1.308895546231238</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.656912192603144</v>
+        <v>8.224066582972988</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09086114172145009</v>
+        <v>0.09076740058177465</v>
       </c>
       <c r="C22">
-        <v>417.7681784758279</v>
+        <v>413.0596992548213</v>
       </c>
       <c r="D22">
-        <v>439.2681784758279</v>
+        <v>439.9196992548213</v>
       </c>
       <c r="E22">
-        <v>-125.8</v>
+        <v>-120.44</v>
       </c>
       <c r="F22">
-        <v>107.2</v>
+        <v>112.56</v>
       </c>
       <c r="G22">
         <v>85.7</v>
@@ -3085,28 +3085,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M22">
-        <v>5.7352</v>
+        <v>6.021960000000001</v>
       </c>
       <c r="N22">
-        <v>41.43146666666667</v>
+        <v>41.14470666666667</v>
       </c>
       <c r="O22">
-        <v>7.043349333333335</v>
+        <v>6.994600133333335</v>
       </c>
       <c r="P22">
-        <v>34.38811733333334</v>
+        <v>34.15010653333334</v>
       </c>
       <c r="Q22">
-        <v>45.48811733333334</v>
+        <v>45.25010653333334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1024751771518126</v>
+        <v>0.1030915830149046</v>
       </c>
       <c r="T22">
-        <v>1.308895546231238</v>
+        <v>1.323131247457382</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.224066582972988</v>
+        <v>7.832444364736176</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09076740058177465</v>
+        <v>0.09081973944209921</v>
       </c>
       <c r="C23">
-        <v>413.0596992548213</v>
+        <v>407.3356949902459</v>
       </c>
       <c r="D23">
-        <v>439.9196992548213</v>
+        <v>439.555694990246</v>
       </c>
       <c r="E23">
-        <v>-120.44</v>
+        <v>-115.08</v>
       </c>
       <c r="F23">
-        <v>112.56</v>
+        <v>117.92</v>
       </c>
       <c r="G23">
         <v>85.7</v>
@@ -3167,45 +3167,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M23">
-        <v>6.02196</v>
+        <v>6.403056</v>
       </c>
       <c r="N23">
-        <v>41.14470666666667</v>
+        <v>40.76361066666667</v>
       </c>
       <c r="O23">
-        <v>6.994600133333335</v>
+        <v>6.929813813333335</v>
       </c>
       <c r="P23">
-        <v>34.15010653333334</v>
+        <v>33.83379685333334</v>
       </c>
       <c r="Q23">
-        <v>45.25010653333334</v>
+        <v>44.93379685333334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1030915830149046</v>
+        <v>0.1037237941565375</v>
       </c>
       <c r="T23">
-        <v>1.323131247457382</v>
+        <v>1.337731966663683</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.17</v>
       </c>
       <c r="W23">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.832444364736178</v>
+        <v>7.366274270702407</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09081973944209921</v>
+        <v>0.0907326383024238</v>
       </c>
       <c r="C24">
-        <v>407.3356949902459</v>
+        <v>402.5817959656966</v>
       </c>
       <c r="D24">
-        <v>439.555694990246</v>
+        <v>440.1617959656966</v>
       </c>
       <c r="E24">
-        <v>-115.08</v>
+        <v>-109.72</v>
       </c>
       <c r="F24">
-        <v>117.92</v>
+        <v>123.28</v>
       </c>
       <c r="G24">
         <v>85.7</v>
@@ -3249,28 +3249,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M24">
-        <v>6.403056</v>
+        <v>6.694104</v>
       </c>
       <c r="N24">
-        <v>40.76361066666667</v>
+        <v>40.47256266666667</v>
       </c>
       <c r="O24">
-        <v>6.929813813333335</v>
+        <v>6.880335653333334</v>
       </c>
       <c r="P24">
-        <v>33.83379685333334</v>
+        <v>33.59222701333334</v>
       </c>
       <c r="Q24">
-        <v>44.93379685333334</v>
+        <v>44.69222701333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1037237941565375</v>
+        <v>0.1043724263667841</v>
       </c>
       <c r="T24">
-        <v>1.337731966663683</v>
+        <v>1.352711925329888</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.366274270702407</v>
+        <v>7.046001476324041</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0907326383024238</v>
+        <v>0.09064553716274835</v>
       </c>
       <c r="C25">
-        <v>402.5817959656966</v>
+        <v>397.8295707478783</v>
       </c>
       <c r="D25">
-        <v>440.1617959656966</v>
+        <v>440.7695707478782</v>
       </c>
       <c r="E25">
-        <v>-109.72</v>
+        <v>-104.36</v>
       </c>
       <c r="F25">
-        <v>123.28</v>
+        <v>128.64</v>
       </c>
       <c r="G25">
         <v>85.7</v>
@@ -3331,28 +3331,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M25">
-        <v>6.694104</v>
+        <v>6.985152000000001</v>
       </c>
       <c r="N25">
-        <v>40.47256266666667</v>
+        <v>40.18151466666667</v>
       </c>
       <c r="O25">
-        <v>6.880335653333334</v>
+        <v>6.830857493333335</v>
       </c>
       <c r="P25">
-        <v>33.59222701333334</v>
+        <v>33.35065717333334</v>
       </c>
       <c r="Q25">
-        <v>44.69222701333334</v>
+        <v>44.45065717333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1043724263667841</v>
+        <v>0.1050381278457215</v>
       </c>
       <c r="T25">
-        <v>1.352711925329888</v>
+        <v>1.368086093434677</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.046001476324041</v>
+        <v>6.752418081477206</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09064553716274835</v>
+        <v>0.09055843602307292</v>
       </c>
       <c r="C26">
-        <v>397.8295707478783</v>
+        <v>393.0790262799472</v>
       </c>
       <c r="D26">
-        <v>440.7695707478782</v>
+        <v>441.3790262799473</v>
       </c>
       <c r="E26">
-        <v>-104.36</v>
+        <v>-99</v>
       </c>
       <c r="F26">
-        <v>128.64</v>
+        <v>134</v>
       </c>
       <c r="G26">
         <v>85.7</v>
@@ -3413,28 +3413,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M26">
-        <v>6.985151999999999</v>
+        <v>7.2762</v>
       </c>
       <c r="N26">
-        <v>40.18151466666667</v>
+        <v>39.89046666666667</v>
       </c>
       <c r="O26">
-        <v>6.830857493333335</v>
+        <v>6.781379333333335</v>
       </c>
       <c r="P26">
-        <v>33.35065717333334</v>
+        <v>33.10908733333333</v>
       </c>
       <c r="Q26">
-        <v>44.45065717333334</v>
+        <v>44.20908733333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1050381278457215</v>
+        <v>0.1057215813640972</v>
       </c>
       <c r="T26">
-        <v>1.368086093434677</v>
+        <v>1.383870239355595</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.752418081477207</v>
+        <v>6.482321358218117</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09055843602307292</v>
+        <v>0.09047133488339749</v>
       </c>
       <c r="C27">
-        <v>393.0790262799472</v>
+        <v>388.3301695435156</v>
       </c>
       <c r="D27">
-        <v>441.3790262799473</v>
+        <v>441.9901695435155</v>
       </c>
       <c r="E27">
-        <v>-99</v>
+        <v>-93.63999999999999</v>
       </c>
       <c r="F27">
-        <v>134</v>
+        <v>139.36</v>
       </c>
       <c r="G27">
         <v>85.7</v>
@@ -3495,28 +3495,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M27">
-        <v>7.2762</v>
+        <v>7.567248000000001</v>
       </c>
       <c r="N27">
-        <v>39.89046666666667</v>
+        <v>39.59941866666667</v>
       </c>
       <c r="O27">
-        <v>6.781379333333335</v>
+        <v>6.731901173333335</v>
       </c>
       <c r="P27">
-        <v>33.10908733333333</v>
+        <v>32.86751749333334</v>
       </c>
       <c r="Q27">
-        <v>44.20908733333334</v>
+        <v>43.96751749333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1057215813640972</v>
+        <v>0.1064235065991858</v>
       </c>
       <c r="T27">
-        <v>1.383870239355595</v>
+        <v>1.400080983814915</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.482321358218117</v>
+        <v>6.233001305978959</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09047133488339749</v>
+        <v>0.09060833374372208</v>
       </c>
       <c r="C28">
-        <v>388.3301695435156</v>
+        <v>382.0096808175731</v>
       </c>
       <c r="D28">
-        <v>441.9901695435155</v>
+        <v>441.0296808175731</v>
       </c>
       <c r="E28">
-        <v>-93.63999999999999</v>
+        <v>-88.28</v>
       </c>
       <c r="F28">
-        <v>139.36</v>
+        <v>144.72</v>
       </c>
       <c r="G28">
         <v>85.7</v>
@@ -3577,45 +3577,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M28">
-        <v>7.567248000000001</v>
+        <v>8.003016000000001</v>
       </c>
       <c r="N28">
-        <v>39.59941866666667</v>
+        <v>39.16365066666667</v>
       </c>
       <c r="O28">
-        <v>6.731901173333335</v>
+        <v>6.657820613333334</v>
       </c>
       <c r="P28">
-        <v>32.86751749333334</v>
+        <v>32.50583005333333</v>
       </c>
       <c r="Q28">
-        <v>43.96751749333334</v>
+        <v>43.60583005333334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1064235065991858</v>
+        <v>0.107144662662633</v>
       </c>
       <c r="T28">
-        <v>1.400080983814915</v>
+        <v>1.416735858259422</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.17</v>
       </c>
       <c r="W28">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.233001305978959</v>
+        <v>5.893611441819767</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09060833374372208</v>
+        <v>0.09052953260404663</v>
       </c>
       <c r="C29">
-        <v>382.0096808175731</v>
+        <v>377.2016390469354</v>
       </c>
       <c r="D29">
-        <v>441.0296808175731</v>
+        <v>441.5816390469354</v>
       </c>
       <c r="E29">
-        <v>-88.28</v>
+        <v>-82.91999999999999</v>
       </c>
       <c r="F29">
-        <v>144.72</v>
+        <v>150.08</v>
       </c>
       <c r="G29">
         <v>85.7</v>
@@ -3659,28 +3659,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M29">
-        <v>8.003016000000001</v>
+        <v>8.299424</v>
       </c>
       <c r="N29">
-        <v>39.16365066666667</v>
+        <v>38.86724266666667</v>
       </c>
       <c r="O29">
-        <v>6.657820613333334</v>
+        <v>6.607431253333334</v>
       </c>
       <c r="P29">
-        <v>32.50583005333333</v>
+        <v>32.25981141333334</v>
       </c>
       <c r="Q29">
-        <v>43.60583005333334</v>
+        <v>43.35981141333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.107144662662633</v>
+        <v>0.1078858508389537</v>
       </c>
       <c r="T29">
-        <v>1.416735858259422</v>
+        <v>1.433853368105166</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.893611441819767</v>
+        <v>5.683125318897633</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09052953260404663</v>
+        <v>0.09045073146437121</v>
       </c>
       <c r="C30">
-        <v>377.2016390469354</v>
+        <v>372.3949805829725</v>
       </c>
       <c r="D30">
-        <v>441.5816390469354</v>
+        <v>442.1349805829726</v>
       </c>
       <c r="E30">
-        <v>-82.91999999999999</v>
+        <v>-77.55999999999997</v>
       </c>
       <c r="F30">
-        <v>150.08</v>
+        <v>155.44</v>
       </c>
       <c r="G30">
         <v>85.7</v>
@@ -3741,28 +3741,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M30">
-        <v>8.299424</v>
+        <v>8.595832000000001</v>
       </c>
       <c r="N30">
-        <v>38.86724266666667</v>
+        <v>38.57083466666667</v>
       </c>
       <c r="O30">
-        <v>6.607431253333334</v>
+        <v>6.557041893333334</v>
       </c>
       <c r="P30">
-        <v>32.25981141333334</v>
+        <v>32.01379277333334</v>
       </c>
       <c r="Q30">
-        <v>43.35981141333334</v>
+        <v>43.11379277333334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1078858508389537</v>
+        <v>0.1086479175554524</v>
       </c>
       <c r="T30">
-        <v>1.433853368105166</v>
+        <v>1.451453061326846</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.683125318897633</v>
+        <v>5.487155480314955</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09045073146437121</v>
+        <v>0.09037193032469577</v>
       </c>
       <c r="C31">
-        <v>372.3949805829726</v>
+        <v>367.5897106324329</v>
       </c>
       <c r="D31">
-        <v>442.1349805829726</v>
+        <v>442.6897106324329</v>
       </c>
       <c r="E31">
-        <v>-77.56</v>
+        <v>-72.20000000000002</v>
       </c>
       <c r="F31">
-        <v>155.44</v>
+        <v>160.8</v>
       </c>
       <c r="G31">
         <v>85.7</v>
@@ -3823,28 +3823,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M31">
-        <v>8.595832</v>
+        <v>8.892239999999999</v>
       </c>
       <c r="N31">
-        <v>38.57083466666667</v>
+        <v>38.27442666666667</v>
       </c>
       <c r="O31">
-        <v>6.557041893333334</v>
+        <v>6.506652533333335</v>
       </c>
       <c r="P31">
-        <v>32.01379277333334</v>
+        <v>31.76777413333334</v>
       </c>
       <c r="Q31">
-        <v>43.11379277333334</v>
+        <v>42.86777413333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1086479175554524</v>
+        <v>0.1094317576067083</v>
       </c>
       <c r="T31">
-        <v>1.451453061326846</v>
+        <v>1.469555602926288</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.487155480314956</v>
+        <v>5.304250297637791</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09037193032469577</v>
+        <v>0.09029312918502035</v>
       </c>
       <c r="C32">
-        <v>367.5897106324329</v>
+        <v>362.7858344282275</v>
       </c>
       <c r="D32">
-        <v>442.6897106324329</v>
+        <v>443.2458344282275</v>
       </c>
       <c r="E32">
-        <v>-72.20000000000002</v>
+        <v>-66.84</v>
       </c>
       <c r="F32">
-        <v>160.8</v>
+        <v>166.16</v>
       </c>
       <c r="G32">
         <v>85.7</v>
@@ -3905,28 +3905,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M32">
-        <v>8.892239999999999</v>
+        <v>9.188648000000001</v>
       </c>
       <c r="N32">
-        <v>38.27442666666667</v>
+        <v>37.97801866666667</v>
       </c>
       <c r="O32">
-        <v>6.506652533333335</v>
+        <v>6.456263173333334</v>
       </c>
       <c r="P32">
-        <v>31.76777413333334</v>
+        <v>31.52175549333334</v>
       </c>
       <c r="Q32">
-        <v>42.86777413333334</v>
+        <v>42.62175549333334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1094317576067083</v>
+        <v>0.1102383176594498</v>
       </c>
       <c r="T32">
-        <v>1.469555602926288</v>
+        <v>1.488182855876439</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.304250297637791</v>
+        <v>5.133145449326895</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09029312918502035</v>
+        <v>0.0902143280453449</v>
       </c>
       <c r="C33">
-        <v>362.7858344282275</v>
+        <v>357.9833572295965</v>
       </c>
       <c r="D33">
-        <v>443.2458344282275</v>
+        <v>443.8033572295965</v>
       </c>
       <c r="E33">
-        <v>-66.84</v>
+        <v>-61.47999999999999</v>
       </c>
       <c r="F33">
-        <v>166.16</v>
+        <v>171.52</v>
       </c>
       <c r="G33">
         <v>85.7</v>
@@ -3987,28 +3987,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M33">
-        <v>9.188648000000001</v>
+        <v>9.485056</v>
       </c>
       <c r="N33">
-        <v>37.97801866666667</v>
+        <v>37.68161066666667</v>
       </c>
       <c r="O33">
-        <v>6.456263173333334</v>
+        <v>6.405873813333335</v>
       </c>
       <c r="P33">
-        <v>31.52175549333334</v>
+        <v>31.27573685333333</v>
       </c>
       <c r="Q33">
-        <v>42.62175549333334</v>
+        <v>42.37573685333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1102383176594498</v>
+        <v>0.1110686000666837</v>
       </c>
       <c r="T33">
-        <v>1.488182855876439</v>
+        <v>1.507357969207476</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.133145449326895</v>
+        <v>4.972734654035429</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0902143280453449</v>
+        <v>0.09013552690566948</v>
       </c>
       <c r="C34">
-        <v>357.9833572295965</v>
+        <v>353.1822843222732</v>
       </c>
       <c r="D34">
-        <v>443.8033572295965</v>
+        <v>444.3622843222731</v>
       </c>
       <c r="E34">
-        <v>-61.47999999999999</v>
+        <v>-56.12</v>
       </c>
       <c r="F34">
-        <v>171.52</v>
+        <v>176.88</v>
       </c>
       <c r="G34">
         <v>85.7</v>
@@ -4069,28 +4069,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M34">
-        <v>9.485056</v>
+        <v>9.781464</v>
       </c>
       <c r="N34">
-        <v>37.68161066666667</v>
+        <v>37.38520266666667</v>
       </c>
       <c r="O34">
-        <v>6.405873813333335</v>
+        <v>6.355484453333335</v>
       </c>
       <c r="P34">
-        <v>31.27573685333333</v>
+        <v>31.02971821333334</v>
       </c>
       <c r="Q34">
-        <v>42.37573685333334</v>
+        <v>42.12971821333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1110686000666837</v>
+        <v>0.1119236670233873</v>
       </c>
       <c r="T34">
-        <v>1.507357969207476</v>
+        <v>1.527105473981231</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.972734654035429</v>
+        <v>4.822045725125265</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09013552690566948</v>
+        <v>0.09005672576599405</v>
       </c>
       <c r="C35">
-        <v>353.1822843222732</v>
+        <v>348.3826210186522</v>
       </c>
       <c r="D35">
-        <v>444.3622843222731</v>
+        <v>444.9226210186523</v>
       </c>
       <c r="E35">
-        <v>-56.12</v>
+        <v>-50.75999999999999</v>
       </c>
       <c r="F35">
-        <v>176.88</v>
+        <v>182.24</v>
       </c>
       <c r="G35">
         <v>85.7</v>
@@ -4151,28 +4151,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M35">
-        <v>9.781464</v>
+        <v>10.077872</v>
       </c>
       <c r="N35">
-        <v>37.38520266666667</v>
+        <v>37.08879466666667</v>
       </c>
       <c r="O35">
-        <v>6.355484453333335</v>
+        <v>6.305095093333335</v>
       </c>
       <c r="P35">
-        <v>31.02971821333334</v>
+        <v>30.78369957333334</v>
       </c>
       <c r="Q35">
-        <v>42.12971821333333</v>
+        <v>41.88369957333334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1119236670233873</v>
+        <v>0.112804645099991</v>
       </c>
       <c r="T35">
-        <v>1.527105473981231</v>
+        <v>1.547451387990555</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.822045725125265</v>
+        <v>4.680220850856874</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09005672576599405</v>
+        <v>0.08997792462631862</v>
       </c>
       <c r="C36">
-        <v>348.3826210186522</v>
+        <v>343.5843726579581</v>
       </c>
       <c r="D36">
-        <v>444.9226210186523</v>
+        <v>445.4843726579581</v>
       </c>
       <c r="E36">
-        <v>-50.75999999999999</v>
+        <v>-45.39999999999998</v>
       </c>
       <c r="F36">
-        <v>182.24</v>
+        <v>187.6</v>
       </c>
       <c r="G36">
         <v>85.7</v>
@@ -4233,28 +4233,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M36">
-        <v>10.077872</v>
+        <v>10.37428</v>
       </c>
       <c r="N36">
-        <v>37.08879466666667</v>
+        <v>36.79238666666667</v>
       </c>
       <c r="O36">
-        <v>6.305095093333335</v>
+        <v>6.254705733333335</v>
       </c>
       <c r="P36">
-        <v>30.78369957333334</v>
+        <v>30.53768093333334</v>
       </c>
       <c r="Q36">
-        <v>41.88369957333334</v>
+        <v>41.63768093333334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.112804645099991</v>
+        <v>0.1137127301943364</v>
       </c>
       <c r="T36">
-        <v>1.547451387990555</v>
+        <v>1.568423330123242</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.680220850856874</v>
+        <v>4.546500255118106</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08997792462631862</v>
+        <v>0.09064612348664319</v>
       </c>
       <c r="C37">
-        <v>343.5843726579581</v>
+        <v>333.5054738828595</v>
       </c>
       <c r="D37">
-        <v>445.4843726579581</v>
+        <v>440.7654738828596</v>
       </c>
       <c r="E37">
-        <v>-45.39999999999998</v>
+        <v>-40.03999999999996</v>
       </c>
       <c r="F37">
-        <v>187.6</v>
+        <v>192.96</v>
       </c>
       <c r="G37">
         <v>85.7</v>
@@ -4315,45 +4315,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M37">
-        <v>10.37428</v>
+        <v>11.153088</v>
       </c>
       <c r="N37">
-        <v>36.79238666666667</v>
+        <v>36.01357866666667</v>
       </c>
       <c r="O37">
-        <v>6.254705733333335</v>
+        <v>6.122308373333334</v>
       </c>
       <c r="P37">
-        <v>30.53768093333334</v>
+        <v>29.89127029333333</v>
       </c>
       <c r="Q37">
-        <v>41.63768093333334</v>
+        <v>40.99127029333334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1137127301943364</v>
+        <v>0.11464919294788</v>
       </c>
       <c r="T37">
-        <v>1.568423330123242</v>
+        <v>1.590050645447576</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.17</v>
       </c>
       <c r="W37">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.546500255118106</v>
+        <v>4.22902308909126</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09064612348664321</v>
+        <v>0.09058807234696777</v>
       </c>
       <c r="C38">
-        <v>333.5054738828596</v>
+        <v>328.5514688272412</v>
       </c>
       <c r="D38">
-        <v>440.7654738828595</v>
+        <v>441.1714688272412</v>
       </c>
       <c r="E38">
-        <v>-40.04000000000002</v>
+        <v>-34.68000000000001</v>
       </c>
       <c r="F38">
-        <v>192.96</v>
+        <v>198.32</v>
       </c>
       <c r="G38">
         <v>85.7</v>
@@ -4397,28 +4397,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M38">
-        <v>11.153088</v>
+        <v>11.462896</v>
       </c>
       <c r="N38">
-        <v>36.01357866666667</v>
+        <v>35.70377066666667</v>
       </c>
       <c r="O38">
-        <v>6.122308373333335</v>
+        <v>6.069641013333334</v>
       </c>
       <c r="P38">
-        <v>29.89127029333334</v>
+        <v>29.63412965333334</v>
       </c>
       <c r="Q38">
-        <v>40.99127029333334</v>
+        <v>40.73412965333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.11464919294788</v>
+        <v>0.1156153846777266</v>
       </c>
       <c r="T38">
-        <v>1.590050645447575</v>
+        <v>1.612364542210777</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.22902308909126</v>
+        <v>4.11472516776447</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09058807234696777</v>
+        <v>0.09053002120729234</v>
       </c>
       <c r="C39">
-        <v>328.5514688272412</v>
+        <v>323.5982123958843</v>
       </c>
       <c r="D39">
-        <v>441.1714688272412</v>
+        <v>441.5782123958843</v>
       </c>
       <c r="E39">
-        <v>-34.68000000000001</v>
+        <v>-29.31999999999999</v>
       </c>
       <c r="F39">
-        <v>198.32</v>
+        <v>203.68</v>
       </c>
       <c r="G39">
         <v>85.7</v>
@@ -4479,28 +4479,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M39">
-        <v>11.462896</v>
+        <v>11.772704</v>
       </c>
       <c r="N39">
-        <v>35.70377066666667</v>
+        <v>35.39396266666667</v>
       </c>
       <c r="O39">
-        <v>6.069641013333334</v>
+        <v>6.016973653333334</v>
       </c>
       <c r="P39">
-        <v>29.63412965333334</v>
+        <v>29.37698901333333</v>
       </c>
       <c r="Q39">
-        <v>40.73412965333334</v>
+        <v>40.47698901333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1156153846777266</v>
+        <v>0.1166127438827296</v>
       </c>
       <c r="T39">
-        <v>1.612364542210777</v>
+        <v>1.635398242095372</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.11472516776447</v>
+        <v>4.00644292650751</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09053002120729234</v>
+        <v>0.09160492006761692</v>
       </c>
       <c r="C40">
-        <v>323.5982123958843</v>
+        <v>310.8263677679451</v>
       </c>
       <c r="D40">
-        <v>441.5782123958843</v>
+        <v>434.1663677679451</v>
       </c>
       <c r="E40">
-        <v>-29.31999999999999</v>
+        <v>-23.95999999999998</v>
       </c>
       <c r="F40">
-        <v>203.68</v>
+        <v>209.04</v>
       </c>
       <c r="G40">
         <v>85.7</v>
@@ -4561,45 +4561,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M40">
-        <v>11.772704</v>
+        <v>12.814152</v>
       </c>
       <c r="N40">
-        <v>35.39396266666667</v>
+        <v>34.35251466666667</v>
       </c>
       <c r="O40">
-        <v>6.016973653333334</v>
+        <v>5.839927493333334</v>
       </c>
       <c r="P40">
-        <v>29.37698901333333</v>
+        <v>28.51258717333334</v>
       </c>
       <c r="Q40">
-        <v>40.47698901333334</v>
+        <v>39.61258717333334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1166127438827296</v>
+        <v>0.1176428033895359</v>
       </c>
       <c r="T40">
-        <v>1.635398242095372</v>
+        <v>1.659187145254871</v>
       </c>
       <c r="U40">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0.17</v>
       </c>
       <c r="W40">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.00644292650751</v>
+        <v>3.680826219844018</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09160492006761692</v>
+        <v>0.09157591892794148</v>
       </c>
       <c r="C41">
-        <v>310.8263677679451</v>
+        <v>305.6630744127187</v>
       </c>
       <c r="D41">
-        <v>434.1663677679451</v>
+        <v>434.3630744127187</v>
       </c>
       <c r="E41">
-        <v>-23.95999999999998</v>
+        <v>-18.59999999999999</v>
       </c>
       <c r="F41">
-        <v>209.04</v>
+        <v>214.4</v>
       </c>
       <c r="G41">
         <v>85.7</v>
@@ -4643,28 +4643,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M41">
-        <v>12.814152</v>
+        <v>13.14272</v>
       </c>
       <c r="N41">
-        <v>34.35251466666667</v>
+        <v>34.02394666666667</v>
       </c>
       <c r="O41">
-        <v>5.839927493333334</v>
+        <v>5.784070933333335</v>
       </c>
       <c r="P41">
-        <v>28.51258717333334</v>
+        <v>28.23987573333334</v>
       </c>
       <c r="Q41">
-        <v>39.61258717333334</v>
+        <v>39.33987573333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1176428033895359</v>
+        <v>0.1187071982132358</v>
       </c>
       <c r="T41">
-        <v>1.659187145254871</v>
+        <v>1.683769011853021</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.680826219844018</v>
+        <v>3.588805564347918</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09157591892794148</v>
+        <v>0.09154691778826607</v>
       </c>
       <c r="C42">
-        <v>305.6630744127187</v>
+        <v>300.4999593810367</v>
       </c>
       <c r="D42">
-        <v>434.3630744127187</v>
+        <v>434.5599593810367</v>
       </c>
       <c r="E42">
-        <v>-18.59999999999999</v>
+        <v>-13.23999999999998</v>
       </c>
       <c r="F42">
-        <v>214.4</v>
+        <v>219.76</v>
       </c>
       <c r="G42">
         <v>85.7</v>
@@ -4725,28 +4725,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M42">
-        <v>13.14272</v>
+        <v>13.471288</v>
       </c>
       <c r="N42">
-        <v>34.02394666666667</v>
+        <v>33.69537866666667</v>
       </c>
       <c r="O42">
-        <v>5.784070933333335</v>
+        <v>5.728214373333334</v>
       </c>
       <c r="P42">
-        <v>28.23987573333334</v>
+        <v>27.96716429333334</v>
       </c>
       <c r="Q42">
-        <v>39.33987573333334</v>
+        <v>39.06716429333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1187071982132358</v>
+        <v>0.1198076742174001</v>
       </c>
       <c r="T42">
-        <v>1.683769011853021</v>
+        <v>1.709184162064668</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.588805564347918</v>
+        <v>3.501273721315042</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09154691778826607</v>
+        <v>0.09249399664859063</v>
       </c>
       <c r="C43">
-        <v>300.4999593810367</v>
+        <v>288.801277126903</v>
       </c>
       <c r="D43">
-        <v>434.5599593810367</v>
+        <v>428.221277126903</v>
       </c>
       <c r="E43">
-        <v>-13.23999999999998</v>
+        <v>-7.879999999999967</v>
       </c>
       <c r="F43">
-        <v>219.76</v>
+        <v>225.12</v>
       </c>
       <c r="G43">
         <v>85.7</v>
@@ -4807,45 +4807,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M43">
-        <v>13.471288</v>
+        <v>14.430192</v>
       </c>
       <c r="N43">
-        <v>33.69537866666667</v>
+        <v>32.73647466666667</v>
       </c>
       <c r="O43">
-        <v>5.728214373333334</v>
+        <v>5.565200693333334</v>
       </c>
       <c r="P43">
-        <v>27.96716429333334</v>
+        <v>27.17127397333333</v>
       </c>
       <c r="Q43">
-        <v>39.06716429333333</v>
+        <v>38.27127397333334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1198076742174001</v>
+        <v>0.1209460976699838</v>
       </c>
       <c r="T43">
-        <v>1.709184162064668</v>
+        <v>1.735475696766371</v>
       </c>
       <c r="U43">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.17</v>
       </c>
       <c r="W43">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.501273721315042</v>
+        <v>3.268609777795518</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09249399664859062</v>
+        <v>0.0924882355089152</v>
       </c>
       <c r="C44">
-        <v>288.8012771269031</v>
+        <v>283.4792766647862</v>
       </c>
       <c r="D44">
-        <v>428.2212771269031</v>
+        <v>428.2592766647862</v>
       </c>
       <c r="E44">
-        <v>-7.879999999999995</v>
+        <v>-2.52000000000001</v>
       </c>
       <c r="F44">
-        <v>225.12</v>
+        <v>230.48</v>
       </c>
       <c r="G44">
         <v>85.7</v>
@@ -4889,28 +4889,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M44">
-        <v>14.430192</v>
+        <v>14.773768</v>
       </c>
       <c r="N44">
-        <v>32.73647466666667</v>
+        <v>32.39289866666667</v>
       </c>
       <c r="O44">
-        <v>5.565200693333334</v>
+        <v>5.506792773333334</v>
       </c>
       <c r="P44">
-        <v>27.17127397333333</v>
+        <v>26.88610589333333</v>
       </c>
       <c r="Q44">
-        <v>38.27127397333334</v>
+        <v>37.98610589333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1209460976699838</v>
+        <v>0.1221244658051144</v>
       </c>
       <c r="T44">
-        <v>1.73547569676637</v>
+        <v>1.762689741457607</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.268609777795518</v>
+        <v>3.192595596916553</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0924882355089152</v>
+        <v>0.09248247436923976</v>
       </c>
       <c r="C45">
-        <v>283.4792766647862</v>
+        <v>278.1572829472806</v>
       </c>
       <c r="D45">
-        <v>428.2592766647862</v>
+        <v>428.2972829472806</v>
       </c>
       <c r="E45">
-        <v>-2.52000000000001</v>
+        <v>2.840000000000003</v>
       </c>
       <c r="F45">
-        <v>230.48</v>
+        <v>235.84</v>
       </c>
       <c r="G45">
         <v>85.7</v>
@@ -4971,28 +4971,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M45">
-        <v>14.773768</v>
+        <v>15.117344</v>
       </c>
       <c r="N45">
-        <v>32.39289866666667</v>
+        <v>32.04932266666667</v>
       </c>
       <c r="O45">
-        <v>5.506792773333334</v>
+        <v>5.448384853333334</v>
       </c>
       <c r="P45">
-        <v>26.88610589333333</v>
+        <v>26.60093781333333</v>
       </c>
       <c r="Q45">
-        <v>37.98610589333333</v>
+        <v>37.70093781333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1221244658051144</v>
+        <v>0.1233449185164996</v>
       </c>
       <c r="T45">
-        <v>1.762689741457607</v>
+        <v>1.790875716316388</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.192595596916553</v>
+        <v>3.12003660607754</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09248247436923976</v>
+        <v>0.09247671322956434</v>
       </c>
       <c r="C46">
-        <v>278.1572829472806</v>
+        <v>272.835295976182</v>
       </c>
       <c r="D46">
-        <v>428.2972829472806</v>
+        <v>428.335295976182</v>
       </c>
       <c r="E46">
-        <v>2.840000000000003</v>
+        <v>8.200000000000017</v>
       </c>
       <c r="F46">
-        <v>235.84</v>
+        <v>241.2</v>
       </c>
       <c r="G46">
         <v>85.7</v>
@@ -5053,28 +5053,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M46">
-        <v>15.117344</v>
+        <v>15.46092</v>
       </c>
       <c r="N46">
-        <v>32.04932266666667</v>
+        <v>31.70574666666667</v>
       </c>
       <c r="O46">
-        <v>5.448384853333334</v>
+        <v>5.389976933333334</v>
       </c>
       <c r="P46">
-        <v>26.60093781333333</v>
+        <v>26.31576973333334</v>
       </c>
       <c r="Q46">
-        <v>37.70093781333334</v>
+        <v>37.41576973333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1233449185164996</v>
+        <v>0.1246097513264806</v>
       </c>
       <c r="T46">
-        <v>1.790875716316388</v>
+        <v>1.820086635715488</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.12003660607754</v>
+        <v>3.050702459275817</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09247671322956434</v>
+        <v>0.09544899208988891</v>
       </c>
       <c r="C47">
-        <v>272.835295976182</v>
+        <v>248.7206968698615</v>
       </c>
       <c r="D47">
-        <v>428.335295976182</v>
+        <v>409.5806968698615</v>
       </c>
       <c r="E47">
-        <v>8.200000000000017</v>
+        <v>13.56</v>
       </c>
       <c r="F47">
-        <v>241.2</v>
+        <v>246.56</v>
       </c>
       <c r="G47">
         <v>85.7</v>
@@ -5135,45 +5135,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M47">
-        <v>15.46092</v>
+        <v>17.727664</v>
       </c>
       <c r="N47">
-        <v>31.70574666666667</v>
+        <v>29.43900266666667</v>
       </c>
       <c r="O47">
-        <v>5.389976933333334</v>
+        <v>5.004630453333334</v>
       </c>
       <c r="P47">
-        <v>26.31576973333334</v>
+        <v>24.43437221333334</v>
       </c>
       <c r="Q47">
-        <v>37.41576973333333</v>
+        <v>35.53437221333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1246097513264806</v>
+        <v>0.1259214297960906</v>
       </c>
       <c r="T47">
-        <v>1.820086635715488</v>
+        <v>1.850379441018258</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.17</v>
       </c>
       <c r="W47">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.050702459275817</v>
+        <v>2.660625035913737</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09544899208988891</v>
+        <v>0.09550797095021349</v>
       </c>
       <c r="C48">
-        <v>248.7206968698615</v>
+        <v>243.0051531059286</v>
       </c>
       <c r="D48">
-        <v>409.5806968698615</v>
+        <v>409.2251531059287</v>
       </c>
       <c r="E48">
-        <v>13.56</v>
+        <v>18.92000000000002</v>
       </c>
       <c r="F48">
-        <v>246.56</v>
+        <v>251.92</v>
       </c>
       <c r="G48">
         <v>85.7</v>
@@ -5217,28 +5217,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M48">
-        <v>17.727664</v>
+        <v>18.113048</v>
       </c>
       <c r="N48">
-        <v>29.43900266666667</v>
+        <v>29.05361866666667</v>
       </c>
       <c r="O48">
-        <v>5.004630453333334</v>
+        <v>4.939115173333334</v>
       </c>
       <c r="P48">
-        <v>24.43437221333334</v>
+        <v>24.11450349333333</v>
       </c>
       <c r="Q48">
-        <v>35.53437221333334</v>
+        <v>35.21450349333334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1259214297960906</v>
+        <v>0.1272826055664405</v>
       </c>
       <c r="T48">
-        <v>1.850379441018258</v>
+        <v>1.881815371049435</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.660625035913737</v>
+        <v>2.604015992596423</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09550797095021349</v>
+        <v>0.09556694981053807</v>
       </c>
       <c r="C49">
-        <v>243.0051531059286</v>
+        <v>237.2902260787247</v>
       </c>
       <c r="D49">
-        <v>409.2251531059287</v>
+        <v>408.8702260787247</v>
       </c>
       <c r="E49">
-        <v>18.92000000000002</v>
+        <v>24.28000000000003</v>
       </c>
       <c r="F49">
-        <v>251.92</v>
+        <v>257.28</v>
       </c>
       <c r="G49">
         <v>85.7</v>
@@ -5299,28 +5299,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M49">
-        <v>18.113048</v>
+        <v>18.498432</v>
       </c>
       <c r="N49">
-        <v>29.05361866666667</v>
+        <v>28.66823466666667</v>
       </c>
       <c r="O49">
-        <v>4.939115173333334</v>
+        <v>4.873599893333334</v>
       </c>
       <c r="P49">
-        <v>24.11450349333333</v>
+        <v>23.79463477333333</v>
       </c>
       <c r="Q49">
-        <v>35.21450349333334</v>
+        <v>34.89463477333334</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1272826055664405</v>
+        <v>0.1286961342510347</v>
       </c>
       <c r="T49">
-        <v>1.881815371049435</v>
+        <v>1.91446037531258</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.604015992596423</v>
+        <v>2.549765659417331</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09556694981053805</v>
+        <v>0.09721205867086262</v>
       </c>
       <c r="C50">
-        <v>237.2902260787249</v>
+        <v>222.2724074004532</v>
       </c>
       <c r="D50">
-        <v>408.8702260787248</v>
+        <v>399.2124074004532</v>
       </c>
       <c r="E50">
-        <v>24.27999999999997</v>
+        <v>29.63999999999999</v>
       </c>
       <c r="F50">
-        <v>257.28</v>
+        <v>262.64</v>
       </c>
       <c r="G50">
         <v>85.7</v>
@@ -5381,45 +5381,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M50">
-        <v>18.498432</v>
+        <v>19.908112</v>
       </c>
       <c r="N50">
-        <v>28.66823466666667</v>
+        <v>27.25855466666667</v>
       </c>
       <c r="O50">
-        <v>4.873599893333334</v>
+        <v>4.633954293333335</v>
       </c>
       <c r="P50">
-        <v>23.79463477333334</v>
+        <v>22.62460037333334</v>
       </c>
       <c r="Q50">
-        <v>34.89463477333334</v>
+        <v>33.72460037333334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1286961342510347</v>
+        <v>0.130165095433064</v>
       </c>
       <c r="T50">
-        <v>1.91446037531258</v>
+        <v>1.948385575821339</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.17</v>
       </c>
       <c r="W50">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.549765659417332</v>
+        <v>2.369218470675003</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09721205867086262</v>
+        <v>0.09730340753118719</v>
       </c>
       <c r="C51">
-        <v>222.2724074004532</v>
+        <v>216.3894854945835</v>
       </c>
       <c r="D51">
-        <v>399.2124074004532</v>
+        <v>398.6894854945836</v>
       </c>
       <c r="E51">
-        <v>29.63999999999999</v>
+        <v>35</v>
       </c>
       <c r="F51">
-        <v>262.64</v>
+        <v>268</v>
       </c>
       <c r="G51">
         <v>85.7</v>
@@ -5463,28 +5463,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M51">
-        <v>19.908112</v>
+        <v>20.3144</v>
       </c>
       <c r="N51">
-        <v>27.25855466666667</v>
+        <v>26.85226666666667</v>
       </c>
       <c r="O51">
-        <v>4.633954293333335</v>
+        <v>4.564885333333334</v>
       </c>
       <c r="P51">
-        <v>22.62460037333334</v>
+        <v>22.28738133333334</v>
       </c>
       <c r="Q51">
-        <v>33.72460037333334</v>
+        <v>33.38738133333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.130165095433064</v>
+        <v>0.1316928150623744</v>
       </c>
       <c r="T51">
-        <v>1.948385575821339</v>
+        <v>1.983667784350448</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.369218470675003</v>
+        <v>2.321834101261502</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09730340753118719</v>
+        <v>0.09739475639151175</v>
       </c>
       <c r="C52">
-        <v>216.3894854945835</v>
+        <v>210.5079317305796</v>
       </c>
       <c r="D52">
-        <v>398.6894854945836</v>
+        <v>398.1679317305797</v>
       </c>
       <c r="E52">
-        <v>35</v>
+        <v>40.36000000000001</v>
       </c>
       <c r="F52">
-        <v>268</v>
+        <v>273.36</v>
       </c>
       <c r="G52">
         <v>85.7</v>
@@ -5545,28 +5545,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M52">
-        <v>20.3144</v>
+        <v>20.720688</v>
       </c>
       <c r="N52">
-        <v>26.85226666666667</v>
+        <v>26.44597866666667</v>
       </c>
       <c r="O52">
-        <v>4.564885333333334</v>
+        <v>4.495816373333334</v>
       </c>
       <c r="P52">
-        <v>22.28738133333334</v>
+        <v>21.95016229333334</v>
       </c>
       <c r="Q52">
-        <v>33.38738133333334</v>
+        <v>33.05016229333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1316928150623744</v>
+        <v>0.133282890594922</v>
       </c>
       <c r="T52">
-        <v>1.983667784350448</v>
+        <v>2.020390083023602</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.321834101261502</v>
+        <v>2.276307942413238</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09739475639151175</v>
+        <v>0.09748610525183632</v>
       </c>
       <c r="C53">
-        <v>210.5079317305796</v>
+        <v>204.6277407461685</v>
       </c>
       <c r="D53">
-        <v>398.1679317305797</v>
+        <v>397.6477407461685</v>
       </c>
       <c r="E53">
-        <v>40.36000000000001</v>
+        <v>45.72000000000003</v>
       </c>
       <c r="F53">
-        <v>273.36</v>
+        <v>278.72</v>
       </c>
       <c r="G53">
         <v>85.7</v>
@@ -5627,28 +5627,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M53">
-        <v>20.720688</v>
+        <v>21.126976</v>
       </c>
       <c r="N53">
-        <v>26.44597866666667</v>
+        <v>26.03969066666667</v>
       </c>
       <c r="O53">
-        <v>4.495816373333334</v>
+        <v>4.426747413333334</v>
       </c>
       <c r="P53">
-        <v>21.95016229333334</v>
+        <v>21.61294325333333</v>
       </c>
       <c r="Q53">
-        <v>33.05016229333334</v>
+        <v>32.71294325333334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.133282890594922</v>
+        <v>0.134939219274659</v>
       </c>
       <c r="T53">
-        <v>2.020390083023602</v>
+        <v>2.058642477474804</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.276307942413238</v>
+        <v>2.232532789674521</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09748610525183632</v>
+        <v>0.09757745411216089</v>
       </c>
       <c r="C54">
-        <v>204.6277407461685</v>
+        <v>198.7489072070628</v>
       </c>
       <c r="D54">
-        <v>397.6477407461685</v>
+        <v>397.1289072070628</v>
       </c>
       <c r="E54">
-        <v>45.72000000000003</v>
+        <v>51.08000000000004</v>
       </c>
       <c r="F54">
-        <v>278.72</v>
+        <v>284.08</v>
       </c>
       <c r="G54">
         <v>85.7</v>
@@ -5709,28 +5709,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M54">
-        <v>21.126976</v>
+        <v>21.53326400000001</v>
       </c>
       <c r="N54">
-        <v>26.03969066666667</v>
+        <v>25.63340266666667</v>
       </c>
       <c r="O54">
-        <v>4.426747413333334</v>
+        <v>4.357678453333333</v>
       </c>
       <c r="P54">
-        <v>21.61294325333333</v>
+        <v>21.27572421333333</v>
       </c>
       <c r="Q54">
-        <v>32.71294325333334</v>
+        <v>32.37572421333333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.134939219274659</v>
+        <v>0.1366660300258742</v>
       </c>
       <c r="T54">
-        <v>2.058642477474804</v>
+        <v>2.098522633392015</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.232532789674521</v>
+        <v>2.190409529491983</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09757745411216089</v>
+        <v>0.09766880297248547</v>
       </c>
       <c r="C55">
-        <v>198.7489072070628</v>
+        <v>192.8714258067787</v>
       </c>
       <c r="D55">
-        <v>397.1289072070628</v>
+        <v>396.6114258067788</v>
       </c>
       <c r="E55">
-        <v>51.08000000000004</v>
+        <v>56.44</v>
       </c>
       <c r="F55">
-        <v>284.08</v>
+        <v>289.44</v>
       </c>
       <c r="G55">
         <v>85.7</v>
@@ -5791,28 +5791,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M55">
-        <v>21.53326400000001</v>
+        <v>21.939552</v>
       </c>
       <c r="N55">
-        <v>25.63340266666667</v>
+        <v>25.22711466666667</v>
       </c>
       <c r="O55">
-        <v>4.357678453333333</v>
+        <v>4.288609493333334</v>
       </c>
       <c r="P55">
-        <v>21.27572421333333</v>
+        <v>20.93850517333333</v>
       </c>
       <c r="Q55">
-        <v>32.37572421333333</v>
+        <v>32.03850517333333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1366660300258742</v>
+        <v>0.1384679195054032</v>
       </c>
       <c r="T55">
-        <v>2.098522633392015</v>
+        <v>2.140136709131714</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.190409529491983</v>
+        <v>2.149846390056947</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09766880297248547</v>
+        <v>0.09776015183281005</v>
       </c>
       <c r="C56">
-        <v>192.8714258067787</v>
+        <v>186.9952912664552</v>
       </c>
       <c r="D56">
-        <v>396.6114258067788</v>
+        <v>396.0952912664553</v>
       </c>
       <c r="E56">
-        <v>56.44</v>
+        <v>61.80000000000001</v>
       </c>
       <c r="F56">
-        <v>289.44</v>
+        <v>294.8</v>
       </c>
       <c r="G56">
         <v>85.7</v>
@@ -5873,28 +5873,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M56">
-        <v>21.939552</v>
+        <v>22.34584</v>
       </c>
       <c r="N56">
-        <v>25.22711466666667</v>
+        <v>24.82082666666667</v>
       </c>
       <c r="O56">
-        <v>4.288609493333334</v>
+        <v>4.219540533333334</v>
       </c>
       <c r="P56">
-        <v>20.93850517333333</v>
+        <v>20.60128613333334</v>
       </c>
       <c r="Q56">
-        <v>32.03850517333333</v>
+        <v>31.70128613333334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1384679195054032</v>
+        <v>0.1403498929618001</v>
       </c>
       <c r="T56">
-        <v>2.140136709131714</v>
+        <v>2.183600299348733</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.149846390056947</v>
+        <v>2.110758273874093</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09776015183281005</v>
+        <v>0.09785150069313461</v>
       </c>
       <c r="C57">
-        <v>186.9952912664552</v>
+        <v>181.1204983346743</v>
       </c>
       <c r="D57">
-        <v>396.0952912664553</v>
+        <v>395.5804983346744</v>
       </c>
       <c r="E57">
-        <v>61.80000000000001</v>
+        <v>67.16000000000003</v>
       </c>
       <c r="F57">
-        <v>294.8</v>
+        <v>300.16</v>
       </c>
       <c r="G57">
         <v>85.7</v>
@@ -5955,28 +5955,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M57">
-        <v>22.34584</v>
+        <v>22.752128</v>
       </c>
       <c r="N57">
-        <v>24.82082666666667</v>
+        <v>24.41453866666667</v>
       </c>
       <c r="O57">
-        <v>4.219540533333334</v>
+        <v>4.150471573333334</v>
       </c>
       <c r="P57">
-        <v>20.60128613333334</v>
+        <v>20.26406709333333</v>
       </c>
       <c r="Q57">
-        <v>31.70128613333334</v>
+        <v>31.36406709333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1403498929618001</v>
+        <v>0.142317410666215</v>
       </c>
       <c r="T57">
-        <v>2.183600299348733</v>
+        <v>2.229039507302888</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.110758273874093</v>
+        <v>2.073066161840627</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09785150069313461</v>
+        <v>0.09794284955345917</v>
       </c>
       <c r="C58">
-        <v>181.1204983346743</v>
+        <v>175.247041787283</v>
       </c>
       <c r="D58">
-        <v>395.5804983346744</v>
+        <v>395.067041787283</v>
       </c>
       <c r="E58">
-        <v>67.16000000000003</v>
+        <v>72.52000000000004</v>
       </c>
       <c r="F58">
-        <v>300.16</v>
+        <v>305.52</v>
       </c>
       <c r="G58">
         <v>85.7</v>
@@ -6037,28 +6037,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M58">
-        <v>22.752128</v>
+        <v>23.15841600000001</v>
       </c>
       <c r="N58">
-        <v>24.41453866666667</v>
+        <v>24.00825066666667</v>
       </c>
       <c r="O58">
-        <v>4.150471573333334</v>
+        <v>4.081402613333333</v>
       </c>
       <c r="P58">
-        <v>20.26406709333333</v>
+        <v>19.92684805333333</v>
       </c>
       <c r="Q58">
-        <v>31.36406709333334</v>
+        <v>31.02684805333333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.142317410666215</v>
+        <v>0.1443764408219981</v>
       </c>
       <c r="T58">
-        <v>2.229039507302888</v>
+        <v>2.276592166789795</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.073066161840627</v>
+        <v>2.036696580053949</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09794284955345917</v>
+        <v>0.09803419841378375</v>
       </c>
       <c r="C59">
-        <v>175.247041787283</v>
+        <v>169.3749164272161</v>
       </c>
       <c r="D59">
-        <v>395.067041787283</v>
+        <v>394.5549164272161</v>
       </c>
       <c r="E59">
-        <v>72.52000000000004</v>
+        <v>77.88000000000005</v>
       </c>
       <c r="F59">
-        <v>305.52</v>
+        <v>310.8800000000001</v>
       </c>
       <c r="G59">
         <v>85.7</v>
@@ -6119,28 +6119,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M59">
-        <v>23.15841600000001</v>
+        <v>23.56470400000001</v>
       </c>
       <c r="N59">
-        <v>24.00825066666667</v>
+        <v>23.60196266666667</v>
       </c>
       <c r="O59">
-        <v>4.081402613333333</v>
+        <v>4.012333653333333</v>
       </c>
       <c r="P59">
-        <v>19.92684805333333</v>
+        <v>19.58962901333333</v>
       </c>
       <c r="Q59">
-        <v>31.02684805333333</v>
+        <v>30.68962901333333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1443764408219981</v>
+        <v>0.1465335200328184</v>
       </c>
       <c r="T59">
-        <v>2.276592166789795</v>
+        <v>2.326409238633221</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.036696580053949</v>
+        <v>2.001581121777157</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09803419841378375</v>
+        <v>0.1050792872741083</v>
       </c>
       <c r="C60">
-        <v>169.3749164272161</v>
+        <v>128.1546341637772</v>
       </c>
       <c r="D60">
-        <v>394.5549164272161</v>
+        <v>358.6946341637772</v>
       </c>
       <c r="E60">
-        <v>77.88</v>
+        <v>83.24000000000001</v>
       </c>
       <c r="F60">
-        <v>310.88</v>
+        <v>316.24</v>
       </c>
       <c r="G60">
         <v>85.7</v>
@@ -6201,45 +6201,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M60">
-        <v>23.564704</v>
+        <v>28.4616</v>
       </c>
       <c r="N60">
-        <v>23.60196266666667</v>
+        <v>18.70506666666667</v>
       </c>
       <c r="O60">
-        <v>4.012333653333334</v>
+        <v>3.179861333333334</v>
       </c>
       <c r="P60">
-        <v>19.58962901333334</v>
+        <v>15.52520533333334</v>
       </c>
       <c r="Q60">
-        <v>30.68962901333334</v>
+        <v>26.62520533333334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1465335200328184</v>
+        <v>0.1487958226197764</v>
       </c>
       <c r="T60">
-        <v>2.326409238633221</v>
+        <v>2.37865641154218</v>
       </c>
       <c r="U60">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V60">
         <v>0.17</v>
       </c>
       <c r="W60">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.001581121777157</v>
+        <v>1.657203624064236</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1050792872741083</v>
+        <v>0.1052884961344329</v>
       </c>
       <c r="C61">
-        <v>128.1546341637772</v>
+        <v>121.8291300045232</v>
       </c>
       <c r="D61">
-        <v>358.6946341637772</v>
+        <v>357.7291300045232</v>
       </c>
       <c r="E61">
-        <v>83.24000000000001</v>
+        <v>88.59999999999997</v>
       </c>
       <c r="F61">
-        <v>316.24</v>
+        <v>321.6</v>
       </c>
       <c r="G61">
         <v>85.7</v>
@@ -6283,28 +6283,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M61">
-        <v>28.4616</v>
+        <v>28.944</v>
       </c>
       <c r="N61">
-        <v>18.70506666666667</v>
+        <v>18.22266666666668</v>
       </c>
       <c r="O61">
-        <v>3.179861333333334</v>
+        <v>3.097853333333335</v>
       </c>
       <c r="P61">
-        <v>15.52520533333334</v>
+        <v>15.12481333333334</v>
       </c>
       <c r="Q61">
-        <v>26.62520533333334</v>
+        <v>26.22481333333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1487958226197764</v>
+        <v>0.1511712403360822</v>
       </c>
       <c r="T61">
-        <v>2.37865641154218</v>
+        <v>2.433515943096587</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.657203624064236</v>
+        <v>1.629583563663166</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1052884961344329</v>
+        <v>0.1054977049947574</v>
       </c>
       <c r="C62">
-        <v>121.8291300045232</v>
+        <v>115.5088096184051</v>
       </c>
       <c r="D62">
-        <v>357.7291300045232</v>
+        <v>356.7688096184051</v>
       </c>
       <c r="E62">
-        <v>88.59999999999997</v>
+        <v>93.95999999999998</v>
       </c>
       <c r="F62">
-        <v>321.6</v>
+        <v>326.96</v>
       </c>
       <c r="G62">
         <v>85.7</v>
@@ -6365,28 +6365,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M62">
-        <v>28.944</v>
+        <v>29.4264</v>
       </c>
       <c r="N62">
-        <v>18.22266666666668</v>
+        <v>17.74026666666667</v>
       </c>
       <c r="O62">
-        <v>3.097853333333335</v>
+        <v>3.015845333333335</v>
       </c>
       <c r="P62">
-        <v>15.12481333333334</v>
+        <v>14.72442133333334</v>
       </c>
       <c r="Q62">
-        <v>26.22481333333334</v>
+        <v>25.82442133333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1511712403360822</v>
+        <v>0.1536684743455319</v>
       </c>
       <c r="T62">
-        <v>2.433515943096587</v>
+        <v>2.491188783961477</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.629583563663166</v>
+        <v>1.60286907901295</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1054977049947574</v>
+        <v>0.105706913855082</v>
       </c>
       <c r="C63">
-        <v>115.5088096184051</v>
+        <v>109.1936313698267</v>
       </c>
       <c r="D63">
-        <v>356.7688096184051</v>
+        <v>355.8136313698267</v>
       </c>
       <c r="E63">
-        <v>93.95999999999998</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="F63">
-        <v>326.96</v>
+        <v>332.32</v>
       </c>
       <c r="G63">
         <v>85.7</v>
@@ -6447,28 +6447,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M63">
-        <v>29.4264</v>
+        <v>29.9088</v>
       </c>
       <c r="N63">
-        <v>17.74026666666667</v>
+        <v>17.25786666666667</v>
       </c>
       <c r="O63">
-        <v>3.015845333333335</v>
+        <v>2.933837333333334</v>
       </c>
       <c r="P63">
-        <v>14.72442133333334</v>
+        <v>14.32402933333334</v>
       </c>
       <c r="Q63">
-        <v>25.82442133333334</v>
+        <v>25.42402933333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1536684743455319</v>
+        <v>0.1562971417239001</v>
       </c>
       <c r="T63">
-        <v>2.491188783961477</v>
+        <v>2.551897037503466</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.60286907901295</v>
+        <v>1.577016351932096</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.105706913855082</v>
+        <v>0.1059161227154066</v>
       </c>
       <c r="C64">
-        <v>109.1936313698267</v>
+        <v>102.883554067886</v>
       </c>
       <c r="D64">
-        <v>355.8136313698267</v>
+        <v>354.863554067886</v>
       </c>
       <c r="E64">
-        <v>99.31999999999999</v>
+        <v>104.68</v>
       </c>
       <c r="F64">
-        <v>332.32</v>
+        <v>337.68</v>
       </c>
       <c r="G64">
         <v>85.7</v>
@@ -6529,28 +6529,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M64">
-        <v>29.9088</v>
+        <v>30.3912</v>
       </c>
       <c r="N64">
-        <v>17.25786666666667</v>
+        <v>16.77546666666667</v>
       </c>
       <c r="O64">
-        <v>2.933837333333334</v>
+        <v>2.851829333333335</v>
       </c>
       <c r="P64">
-        <v>14.32402933333334</v>
+        <v>13.92363733333334</v>
       </c>
       <c r="Q64">
-        <v>25.42402933333334</v>
+        <v>25.02363733333334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1562971417239001</v>
+        <v>0.1590678992308286</v>
       </c>
       <c r="T64">
-        <v>2.551897037503466</v>
+        <v>2.615886818263941</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.577016351932096</v>
+        <v>1.551984346345872</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1059161227154066</v>
+        <v>0.1061253315757312</v>
       </c>
       <c r="C65">
-        <v>102.883554067886</v>
+        <v>96.57853696045339</v>
       </c>
       <c r="D65">
-        <v>354.863554067886</v>
+        <v>353.9185369604534</v>
       </c>
       <c r="E65">
-        <v>104.68</v>
+        <v>110.04</v>
       </c>
       <c r="F65">
-        <v>337.68</v>
+        <v>343.04</v>
       </c>
       <c r="G65">
         <v>85.7</v>
@@ -6611,28 +6611,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M65">
-        <v>30.3912</v>
+        <v>30.8736</v>
       </c>
       <c r="N65">
-        <v>16.77546666666667</v>
+        <v>16.29306666666667</v>
       </c>
       <c r="O65">
-        <v>2.851829333333335</v>
+        <v>2.769821333333335</v>
       </c>
       <c r="P65">
-        <v>13.92363733333334</v>
+        <v>13.52324533333334</v>
       </c>
       <c r="Q65">
-        <v>25.02363733333334</v>
+        <v>24.62324533333334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1590678992308286</v>
+        <v>0.1619925877103643</v>
       </c>
       <c r="T65">
-        <v>2.615886818263941</v>
+        <v>2.683431586844442</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.551984346345872</v>
+        <v>1.527734590934218</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1061253315757312</v>
+        <v>0.1063345404360557</v>
       </c>
       <c r="C66">
-        <v>96.57853696045339</v>
+        <v>90.27853972834521</v>
       </c>
       <c r="D66">
-        <v>353.9185369604534</v>
+        <v>352.9785397283453</v>
       </c>
       <c r="E66">
-        <v>110.04</v>
+        <v>115.4</v>
       </c>
       <c r="F66">
-        <v>343.04</v>
+        <v>348.4</v>
       </c>
       <c r="G66">
         <v>85.7</v>
@@ -6693,28 +6693,28 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M66">
-        <v>30.8736</v>
+        <v>31.356</v>
       </c>
       <c r="N66">
-        <v>16.29306666666667</v>
+        <v>15.81066666666667</v>
       </c>
       <c r="O66">
-        <v>2.769821333333335</v>
+        <v>2.687813333333334</v>
       </c>
       <c r="P66">
-        <v>13.52324533333334</v>
+        <v>13.12285333333334</v>
       </c>
       <c r="Q66">
-        <v>24.62324533333334</v>
+        <v>24.22285333333334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1619925877103643</v>
+        <v>0.1650844012458736</v>
       </c>
       <c r="T66">
-        <v>2.683431586844442</v>
+        <v>2.754836056486688</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.527734590934218</v>
+        <v>1.504230981842922</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1063345404360557</v>
+        <v>0.1396534025190487</v>
       </c>
       <c r="C67">
-        <v>90.27853972834521</v>
+        <v>-20.00642680702015</v>
       </c>
       <c r="D67">
-        <v>352.9785397283453</v>
+        <v>248.0535731929799</v>
       </c>
       <c r="E67">
-        <v>115.4</v>
+        <v>120.76</v>
       </c>
       <c r="F67">
-        <v>348.4</v>
+        <v>353.76</v>
       </c>
       <c r="G67">
         <v>85.7</v>
@@ -6775,45 +6775,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M67">
-        <v>31.356</v>
+        <v>51.931968</v>
       </c>
       <c r="N67">
-        <v>15.81066666666667</v>
+        <v>-4.765301333333333</v>
       </c>
       <c r="O67">
-        <v>2.687813333333334</v>
+        <v>-0.8101012266666667</v>
       </c>
       <c r="P67">
-        <v>13.12285333333334</v>
+        <v>-3.955200106666667</v>
       </c>
       <c r="Q67">
-        <v>24.22285333333334</v>
+        <v>7.144799893333335</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1650844012458736</v>
+        <v>0.1697793518631664</v>
       </c>
       <c r="T67">
-        <v>2.754836056486688</v>
+        <v>2.863264477209386</v>
       </c>
       <c r="U67">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.17</v>
+        <v>0.1544007216004857</v>
       </c>
       <c r="W67">
-        <v>0.07469999999999999</v>
+        <v>0.1241339740690487</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.504230981842922</v>
+        <v>0.9082395388263866</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1396534025190487</v>
+        <v>0.1406634025190487</v>
       </c>
       <c r="C68">
-        <v>-20.00642680702015</v>
+        <v>-27.58161912759425</v>
       </c>
       <c r="D68">
-        <v>248.0535731929799</v>
+        <v>245.8383808724057</v>
       </c>
       <c r="E68">
-        <v>120.76</v>
+        <v>126.12</v>
       </c>
       <c r="F68">
-        <v>353.76</v>
+        <v>359.12</v>
       </c>
       <c r="G68">
         <v>85.7</v>
@@ -6857,37 +6857,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M68">
-        <v>51.931968</v>
+        <v>52.718816</v>
       </c>
       <c r="N68">
-        <v>-4.765301333333333</v>
+        <v>-5.552149333333332</v>
       </c>
       <c r="O68">
-        <v>-0.8101012266666667</v>
+        <v>-0.9438653866666666</v>
       </c>
       <c r="P68">
-        <v>-3.955200106666667</v>
+        <v>-4.608283946666666</v>
       </c>
       <c r="Q68">
-        <v>7.144799893333335</v>
+        <v>6.491716053333335</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1697793518631664</v>
+        <v>0.173536301919626</v>
       </c>
       <c r="T68">
-        <v>2.863264477209386</v>
+        <v>2.950030067427852</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1544007216004857</v>
+        <v>0.1520962332183889</v>
       </c>
       <c r="W68">
-        <v>0.1241339740690487</v>
+        <v>0.1244722729635405</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9082395388263866</v>
+        <v>0.8946837248140525</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1406634025190487</v>
+        <v>0.1416734025190487</v>
       </c>
       <c r="C69">
-        <v>-27.58161912759425</v>
+        <v>-35.11759699000714</v>
       </c>
       <c r="D69">
-        <v>245.8383808724057</v>
+        <v>243.6624030099929</v>
       </c>
       <c r="E69">
-        <v>126.12</v>
+        <v>131.48</v>
       </c>
       <c r="F69">
-        <v>359.12</v>
+        <v>364.48</v>
       </c>
       <c r="G69">
         <v>85.7</v>
@@ -6939,37 +6939,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M69">
-        <v>52.718816</v>
+        <v>53.50566400000001</v>
       </c>
       <c r="N69">
-        <v>-5.552149333333332</v>
+        <v>-6.338997333333339</v>
       </c>
       <c r="O69">
-        <v>-0.9438653866666666</v>
+        <v>-1.077629546666668</v>
       </c>
       <c r="P69">
-        <v>-4.608283946666666</v>
+        <v>-5.261367786666671</v>
       </c>
       <c r="Q69">
-        <v>6.491716053333335</v>
+        <v>5.83863221333333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.173536301919626</v>
+        <v>0.1775280613546143</v>
       </c>
       <c r="T69">
-        <v>2.950030067427852</v>
+        <v>3.042218507034972</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1520962332183889</v>
+        <v>0.1498595239063538</v>
       </c>
       <c r="W69">
-        <v>0.1244722729635405</v>
+        <v>0.1248006218905473</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8946837248140525</v>
+        <v>0.8815266112138458</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1416734025190487</v>
+        <v>0.1426834025190487</v>
       </c>
       <c r="C70">
-        <v>-35.11759699000714</v>
+        <v>-42.61539254973525</v>
       </c>
       <c r="D70">
-        <v>243.6624030099929</v>
+        <v>241.5246074502648</v>
       </c>
       <c r="E70">
-        <v>131.48</v>
+        <v>136.84</v>
       </c>
       <c r="F70">
-        <v>364.48</v>
+        <v>369.84</v>
       </c>
       <c r="G70">
         <v>85.7</v>
@@ -7021,37 +7021,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M70">
-        <v>53.50566400000001</v>
+        <v>54.29251200000001</v>
       </c>
       <c r="N70">
-        <v>-6.338997333333339</v>
+        <v>-7.125845333333338</v>
       </c>
       <c r="O70">
-        <v>-1.077629546666668</v>
+        <v>-1.211393706666668</v>
       </c>
       <c r="P70">
-        <v>-5.261367786666671</v>
+        <v>-5.91445162666667</v>
       </c>
       <c r="Q70">
-        <v>5.83863221333333</v>
+        <v>5.185548373333331</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1775280613546143</v>
+        <v>0.181777353656376</v>
       </c>
       <c r="T70">
-        <v>3.042218507034972</v>
+        <v>3.140354587907068</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1498595239063538</v>
+        <v>0.1476876467482907</v>
       </c>
       <c r="W70">
-        <v>0.1248006218905473</v>
+        <v>0.1251194534573509</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8815266112138458</v>
+        <v>0.8687508632252393</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1426834025190487</v>
+        <v>0.1436934025190487</v>
       </c>
       <c r="C71">
-        <v>-42.61539254973525</v>
+        <v>-50.07600205443333</v>
       </c>
       <c r="D71">
-        <v>241.5246074502648</v>
+        <v>239.4239979455667</v>
       </c>
       <c r="E71">
-        <v>136.84</v>
+        <v>142.2</v>
       </c>
       <c r="F71">
-        <v>369.84</v>
+        <v>375.2</v>
       </c>
       <c r="G71">
         <v>85.7</v>
@@ -7103,37 +7103,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M71">
-        <v>54.29251200000001</v>
+        <v>55.07936000000001</v>
       </c>
       <c r="N71">
-        <v>-7.125845333333338</v>
+        <v>-7.912693333333337</v>
       </c>
       <c r="O71">
-        <v>-1.211393706666668</v>
+        <v>-1.345157866666667</v>
       </c>
       <c r="P71">
-        <v>-5.91445162666667</v>
+        <v>-6.567535466666669</v>
       </c>
       <c r="Q71">
-        <v>5.185548373333331</v>
+        <v>4.532464533333332</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.181777353656376</v>
+        <v>0.1863099321115886</v>
       </c>
       <c r="T71">
-        <v>3.140354587907068</v>
+        <v>3.245033074170637</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1476876467482907</v>
+        <v>0.1455778232233151</v>
       </c>
       <c r="W71">
-        <v>0.1251194534573509</v>
+        <v>0.1254291755508173</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8687508632252393</v>
+        <v>0.8563401366077359</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1436934025190487</v>
+        <v>0.1447034025190487</v>
       </c>
       <c r="C72">
-        <v>-50.07600205443333</v>
+        <v>-57.50038739197527</v>
       </c>
       <c r="D72">
-        <v>239.4239979455667</v>
+        <v>237.3596126080248</v>
       </c>
       <c r="E72">
-        <v>142.2</v>
+        <v>147.5600000000001</v>
       </c>
       <c r="F72">
-        <v>375.2</v>
+        <v>380.5600000000001</v>
       </c>
       <c r="G72">
         <v>85.7</v>
@@ -7185,37 +7185,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M72">
-        <v>55.07936000000001</v>
+        <v>55.86620800000001</v>
       </c>
       <c r="N72">
-        <v>-7.912693333333337</v>
+        <v>-8.699541333333343</v>
       </c>
       <c r="O72">
-        <v>-1.345157866666667</v>
+        <v>-1.478922026666668</v>
       </c>
       <c r="P72">
-        <v>-6.567535466666669</v>
+        <v>-7.220619306666674</v>
       </c>
       <c r="Q72">
-        <v>4.532464533333332</v>
+        <v>3.879380693333327</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1863099321115886</v>
+        <v>0.191155102184402</v>
       </c>
       <c r="T72">
-        <v>3.245033074170637</v>
+        <v>3.356930766383418</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1455778232233151</v>
+        <v>0.1435274313469304</v>
       </c>
       <c r="W72">
-        <v>0.1254291755508173</v>
+        <v>0.1257301730782706</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8563401366077359</v>
+        <v>0.8442790079231198</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1447034025190487</v>
+        <v>0.1457134025190487</v>
       </c>
       <c r="C73">
-        <v>-57.50038739197521</v>
+        <v>-64.88947755909169</v>
       </c>
       <c r="D73">
-        <v>237.3596126080248</v>
+        <v>235.3305224409083</v>
       </c>
       <c r="E73">
-        <v>147.56</v>
+        <v>152.92</v>
       </c>
       <c r="F73">
-        <v>380.56</v>
+        <v>385.92</v>
       </c>
       <c r="G73">
         <v>85.7</v>
@@ -7267,37 +7267,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M73">
-        <v>55.86620800000001</v>
+        <v>56.653056</v>
       </c>
       <c r="N73">
-        <v>-8.699541333333336</v>
+        <v>-9.486389333333328</v>
       </c>
       <c r="O73">
-        <v>-1.478922026666667</v>
+        <v>-1.612686186666666</v>
       </c>
       <c r="P73">
-        <v>-7.220619306666669</v>
+        <v>-7.873703146666662</v>
       </c>
       <c r="Q73">
-        <v>3.879380693333332</v>
+        <v>3.22629685333334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1911551021844019</v>
+        <v>0.1963463558338449</v>
       </c>
       <c r="T73">
-        <v>3.356930766383417</v>
+        <v>3.476821150897111</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1435274313469304</v>
+        <v>0.1415339948004453</v>
       </c>
       <c r="W73">
-        <v>0.1257301730782706</v>
+        <v>0.1260228095632946</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8442790079231199</v>
+        <v>0.8325529105908545</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1457134025190487</v>
+        <v>0.1467234025190487</v>
       </c>
       <c r="C74">
-        <v>-64.88947755909169</v>
+        <v>-72.24417005531933</v>
       </c>
       <c r="D74">
-        <v>235.3305224409083</v>
+        <v>233.3358299446807</v>
       </c>
       <c r="E74">
-        <v>152.92</v>
+        <v>158.28</v>
       </c>
       <c r="F74">
-        <v>385.92</v>
+        <v>391.28</v>
       </c>
       <c r="G74">
         <v>85.7</v>
@@ -7349,37 +7349,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M74">
-        <v>56.653056</v>
+        <v>57.439904</v>
       </c>
       <c r="N74">
-        <v>-9.486389333333328</v>
+        <v>-10.27323733333333</v>
       </c>
       <c r="O74">
-        <v>-1.612686186666666</v>
+        <v>-1.746450346666666</v>
       </c>
       <c r="P74">
-        <v>-7.873703146666662</v>
+        <v>-8.526786986666661</v>
       </c>
       <c r="Q74">
-        <v>3.22629685333334</v>
+        <v>2.573213013333341</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1963463558338449</v>
+        <v>0.2019221467906539</v>
       </c>
       <c r="T74">
-        <v>3.476821150897111</v>
+        <v>3.60559230463404</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1415339948004453</v>
+        <v>0.1395951729538638</v>
       </c>
       <c r="W74">
-        <v>0.1260228095632946</v>
+        <v>0.1263074286103728</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8325529105908545</v>
+        <v>0.8211480761991989</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1467234025190487</v>
+        <v>0.1477334025190487</v>
       </c>
       <c r="C75">
-        <v>-72.24417005531933</v>
+        <v>-79.56533220665239</v>
       </c>
       <c r="D75">
-        <v>233.3358299446807</v>
+        <v>231.3746677933476</v>
       </c>
       <c r="E75">
-        <v>158.28</v>
+        <v>163.64</v>
       </c>
       <c r="F75">
-        <v>391.28</v>
+        <v>396.64</v>
       </c>
       <c r="G75">
         <v>85.7</v>
@@ -7431,37 +7431,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M75">
-        <v>57.439904</v>
+        <v>58.226752</v>
       </c>
       <c r="N75">
-        <v>-10.27323733333333</v>
+        <v>-11.06008533333333</v>
       </c>
       <c r="O75">
-        <v>-1.746450346666666</v>
+        <v>-1.880214506666667</v>
       </c>
       <c r="P75">
-        <v>-8.526786986666661</v>
+        <v>-9.179870826666667</v>
       </c>
       <c r="Q75">
-        <v>2.573213013333341</v>
+        <v>1.920129173333335</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2019221467906539</v>
+        <v>0.2079268447441406</v>
       </c>
       <c r="T75">
-        <v>3.60559230463404</v>
+        <v>3.744268931735349</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1395951729538638</v>
+        <v>0.1377087516977305</v>
       </c>
       <c r="W75">
-        <v>0.1263074286103728</v>
+        <v>0.1265843552507732</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8211480761991989</v>
+        <v>0.8100514805748853</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1477334025190487</v>
+        <v>0.1905296633935509</v>
       </c>
       <c r="C76">
-        <v>-79.56533220665239</v>
+        <v>-145.6868924030616</v>
       </c>
       <c r="D76">
-        <v>231.3746677933476</v>
+        <v>170.6131075969384</v>
       </c>
       <c r="E76">
-        <v>163.64</v>
+        <v>169</v>
       </c>
       <c r="F76">
-        <v>396.64</v>
+        <v>402</v>
       </c>
       <c r="G76">
         <v>85.7</v>
@@ -7513,45 +7513,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M76">
-        <v>58.226752</v>
+        <v>80.72160000000001</v>
       </c>
       <c r="N76">
-        <v>-11.06008533333333</v>
+        <v>-33.55493333333334</v>
       </c>
       <c r="O76">
-        <v>-1.880214506666667</v>
+        <v>-5.704338666666668</v>
       </c>
       <c r="P76">
-        <v>-9.179870826666667</v>
+        <v>-27.85059466666667</v>
       </c>
       <c r="Q76">
-        <v>1.920129173333335</v>
+        <v>-16.75059466666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2079268447441406</v>
+        <v>0.2195569620319149</v>
       </c>
       <c r="T76">
-        <v>3.744268931735349</v>
+        <v>4.012862864478405</v>
       </c>
       <c r="U76">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1377087516977305</v>
+        <v>0.09933318137070293</v>
       </c>
       <c r="W76">
-        <v>0.1265843552507732</v>
+        <v>0.1808538971807629</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.8100514805748853</v>
+        <v>0.5843128315923701</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1905296633935509</v>
+        <v>0.1920796633935509</v>
       </c>
       <c r="C77">
-        <v>-145.6868924030616</v>
+        <v>-152.6543524888227</v>
       </c>
       <c r="D77">
-        <v>170.6131075969384</v>
+        <v>169.0056475111773</v>
       </c>
       <c r="E77">
-        <v>169</v>
+        <v>174.36</v>
       </c>
       <c r="F77">
-        <v>402</v>
+        <v>407.36</v>
       </c>
       <c r="G77">
         <v>85.7</v>
@@ -7595,37 +7595,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M77">
-        <v>80.72160000000001</v>
+        <v>81.797888</v>
       </c>
       <c r="N77">
-        <v>-33.55493333333334</v>
+        <v>-34.63122133333333</v>
       </c>
       <c r="O77">
-        <v>-5.704338666666668</v>
+        <v>-5.887307626666666</v>
       </c>
       <c r="P77">
-        <v>-27.85059466666667</v>
+        <v>-28.74391370666666</v>
       </c>
       <c r="Q77">
-        <v>-16.75059466666667</v>
+        <v>-17.64391370666666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2195569620319149</v>
+        <v>0.2267968354499114</v>
       </c>
       <c r="T77">
-        <v>4.012862864478405</v>
+        <v>4.180065483831672</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.09933318137070293</v>
+        <v>0.0980261658263516</v>
       </c>
       <c r="W77">
-        <v>0.1808538971807629</v>
+        <v>0.1811163459020686</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5843128315923701</v>
+        <v>0.5766245048608917</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1920796633935509</v>
+        <v>0.1936296633935509</v>
       </c>
       <c r="C78">
-        <v>-152.6543524888227</v>
+        <v>-159.5918053813422</v>
       </c>
       <c r="D78">
-        <v>169.0056475111773</v>
+        <v>167.4281946186578</v>
       </c>
       <c r="E78">
-        <v>174.36</v>
+        <v>179.72</v>
       </c>
       <c r="F78">
-        <v>407.36</v>
+        <v>412.72</v>
       </c>
       <c r="G78">
         <v>85.7</v>
@@ -7677,37 +7677,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M78">
-        <v>81.797888</v>
+        <v>82.87417600000001</v>
       </c>
       <c r="N78">
-        <v>-34.63122133333333</v>
+        <v>-35.70750933333333</v>
       </c>
       <c r="O78">
-        <v>-5.887307626666666</v>
+        <v>-6.070276586666667</v>
       </c>
       <c r="P78">
-        <v>-28.74391370666666</v>
+        <v>-29.63723274666667</v>
       </c>
       <c r="Q78">
-        <v>-17.64391370666666</v>
+        <v>-18.53723274666667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2267968354499114</v>
+        <v>0.2346662630781684</v>
       </c>
       <c r="T78">
-        <v>4.180065483831672</v>
+        <v>4.361807461389571</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.0980261658263516</v>
+        <v>0.09675309873769766</v>
       </c>
       <c r="W78">
-        <v>0.1811163459020686</v>
+        <v>0.1813719777734703</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5766245048608917</v>
+        <v>0.5691358749276333</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1936296633935509</v>
+        <v>0.1951796633935509</v>
       </c>
       <c r="C79">
-        <v>-159.5918053813422</v>
+        <v>-166.5000835476171</v>
       </c>
       <c r="D79">
-        <v>167.4281946186578</v>
+        <v>165.879916452383</v>
       </c>
       <c r="E79">
-        <v>179.72</v>
+        <v>185.08</v>
       </c>
       <c r="F79">
-        <v>412.72</v>
+        <v>418.08</v>
       </c>
       <c r="G79">
         <v>85.7</v>
@@ -7759,37 +7759,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M79">
-        <v>82.87417600000001</v>
+        <v>83.95046400000001</v>
       </c>
       <c r="N79">
-        <v>-35.70750933333333</v>
+        <v>-36.78379733333334</v>
       </c>
       <c r="O79">
-        <v>-6.070276586666667</v>
+        <v>-6.253245546666668</v>
       </c>
       <c r="P79">
-        <v>-29.63723274666667</v>
+        <v>-30.53055178666667</v>
       </c>
       <c r="Q79">
-        <v>-18.53723274666667</v>
+        <v>-19.43055178666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2346662630781684</v>
+        <v>0.2432510932180851</v>
       </c>
       <c r="T79">
-        <v>4.361807461389571</v>
+        <v>4.560071436907279</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.09675309873769766</v>
+        <v>0.09551267439490665</v>
       </c>
       <c r="W79">
-        <v>0.1813719777734703</v>
+        <v>0.1816210549815027</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5691358749276333</v>
+        <v>0.5618392611465097</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1951796633935509</v>
+        <v>0.1967296633935509</v>
       </c>
       <c r="C80">
-        <v>-166.5000835476171</v>
+        <v>-173.3799889441133</v>
       </c>
       <c r="D80">
-        <v>165.879916452383</v>
+        <v>164.3600110558866</v>
       </c>
       <c r="E80">
-        <v>185.08</v>
+        <v>190.44</v>
       </c>
       <c r="F80">
-        <v>418.08</v>
+        <v>423.44</v>
       </c>
       <c r="G80">
         <v>85.7</v>
@@ -7841,37 +7841,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M80">
-        <v>83.95046400000001</v>
+        <v>85.026752</v>
       </c>
       <c r="N80">
-        <v>-36.78379733333334</v>
+        <v>-37.86008533333333</v>
       </c>
       <c r="O80">
-        <v>-6.253245546666668</v>
+        <v>-6.436214506666667</v>
       </c>
       <c r="P80">
-        <v>-30.53055178666667</v>
+        <v>-31.42387082666666</v>
       </c>
       <c r="Q80">
-        <v>-19.43055178666667</v>
+        <v>-20.32387082666666</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2432510932180851</v>
+        <v>0.2526535262284701</v>
       </c>
       <c r="T80">
-        <v>4.560071436907279</v>
+        <v>4.777217695807625</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.09551267439490665</v>
+        <v>0.09430365320003443</v>
       </c>
       <c r="W80">
-        <v>0.1816210549815027</v>
+        <v>0.1818638264374331</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5618392611465097</v>
+        <v>0.5547273717649084</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1967296633935509</v>
+        <v>0.1982796633935509</v>
       </c>
       <c r="C81">
-        <v>-173.3799889441133</v>
+        <v>-180.2322944018667</v>
       </c>
       <c r="D81">
-        <v>164.3600110558866</v>
+        <v>162.8677055981333</v>
       </c>
       <c r="E81">
-        <v>190.44</v>
+        <v>195.8</v>
       </c>
       <c r="F81">
-        <v>423.44</v>
+        <v>428.8</v>
       </c>
       <c r="G81">
         <v>85.7</v>
@@ -7923,37 +7923,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M81">
-        <v>85.026752</v>
+        <v>86.10304000000001</v>
       </c>
       <c r="N81">
-        <v>-37.86008533333333</v>
+        <v>-38.93637333333334</v>
       </c>
       <c r="O81">
-        <v>-6.436214506666667</v>
+        <v>-6.619183466666668</v>
       </c>
       <c r="P81">
-        <v>-31.42387082666666</v>
+        <v>-32.31718986666667</v>
       </c>
       <c r="Q81">
-        <v>-20.32387082666666</v>
+        <v>-21.21718986666666</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2526535262284701</v>
+        <v>0.2629962025398936</v>
       </c>
       <c r="T81">
-        <v>4.777217695807625</v>
+        <v>5.016078580598007</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.09430365320003443</v>
+        <v>0.09312485753503401</v>
       </c>
       <c r="W81">
-        <v>0.1818638264374331</v>
+        <v>0.1821005286069652</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5547273717649084</v>
+        <v>0.5477932796178471</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1982796633935509</v>
+        <v>0.1998296633935509</v>
       </c>
       <c r="C82">
-        <v>-180.2322944018667</v>
+        <v>-187.0577449368063</v>
       </c>
       <c r="D82">
-        <v>162.8677055981333</v>
+        <v>161.4022550631937</v>
       </c>
       <c r="E82">
-        <v>195.8</v>
+        <v>201.16</v>
       </c>
       <c r="F82">
-        <v>428.8</v>
+        <v>434.16</v>
       </c>
       <c r="G82">
         <v>85.7</v>
@@ -8005,37 +8005,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M82">
-        <v>86.10304000000001</v>
+        <v>87.17932800000001</v>
       </c>
       <c r="N82">
-        <v>-38.93637333333334</v>
+        <v>-40.01266133333334</v>
       </c>
       <c r="O82">
-        <v>-6.619183466666668</v>
+        <v>-6.802152426666669</v>
       </c>
       <c r="P82">
-        <v>-32.31718986666667</v>
+        <v>-33.21050890666667</v>
       </c>
       <c r="Q82">
-        <v>-21.21718986666666</v>
+        <v>-22.11050890666667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2629962025398936</v>
+        <v>0.2744275816209407</v>
       </c>
       <c r="T82">
-        <v>5.016078580598007</v>
+        <v>5.280082716418955</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.09312485753503401</v>
+        <v>0.09197516793583604</v>
       </c>
       <c r="W82">
-        <v>0.1821005286069652</v>
+        <v>0.1823313862784841</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5477932796178471</v>
+        <v>0.5410303996225649</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1998296633935509</v>
+        <v>0.2013796633935509</v>
       </c>
       <c r="C83">
-        <v>-187.0577449368063</v>
+        <v>-193.8570589899683</v>
       </c>
       <c r="D83">
-        <v>161.4022550631937</v>
+        <v>159.9629410100317</v>
       </c>
       <c r="E83">
-        <v>201.16</v>
+        <v>206.52</v>
       </c>
       <c r="F83">
-        <v>434.16</v>
+        <v>439.52</v>
       </c>
       <c r="G83">
         <v>85.7</v>
@@ -8087,37 +8087,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M83">
-        <v>87.17932800000001</v>
+        <v>88.25561600000002</v>
       </c>
       <c r="N83">
-        <v>-40.01266133333334</v>
+        <v>-41.08894933333335</v>
       </c>
       <c r="O83">
-        <v>-6.802152426666669</v>
+        <v>-6.98512138666667</v>
       </c>
       <c r="P83">
-        <v>-33.21050890666667</v>
+        <v>-34.10382794666668</v>
       </c>
       <c r="Q83">
-        <v>-22.11050890666667</v>
+        <v>-23.00382794666668</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2744275816209407</v>
+        <v>0.2871291139332152</v>
       </c>
       <c r="T83">
-        <v>5.280082716418955</v>
+        <v>5.573420645108897</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.09197516793583604</v>
+        <v>0.09085351954637462</v>
       </c>
       <c r="W83">
-        <v>0.1823313862784841</v>
+        <v>0.182556613275088</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5410303996225649</v>
+        <v>0.5344324679198507</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2013796633935509</v>
+        <v>0.2029296633935509</v>
       </c>
       <c r="C84">
-        <v>-193.8570589899683</v>
+        <v>-200.6309296019393</v>
       </c>
       <c r="D84">
-        <v>159.9629410100317</v>
+        <v>158.5490703980607</v>
       </c>
       <c r="E84">
-        <v>206.52</v>
+        <v>211.8800000000001</v>
       </c>
       <c r="F84">
-        <v>439.52</v>
+        <v>444.8800000000001</v>
       </c>
       <c r="G84">
         <v>85.7</v>
@@ -8169,37 +8169,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M84">
-        <v>88.25561600000002</v>
+        <v>89.33190400000001</v>
       </c>
       <c r="N84">
-        <v>-41.08894933333335</v>
+        <v>-42.16523733333334</v>
       </c>
       <c r="O84">
-        <v>-6.98512138666667</v>
+        <v>-7.168090346666668</v>
       </c>
       <c r="P84">
-        <v>-34.10382794666668</v>
+        <v>-34.99714698666667</v>
       </c>
       <c r="Q84">
-        <v>-23.00382794666668</v>
+        <v>-23.89714698666667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2871291139332152</v>
+        <v>0.3013249441645808</v>
       </c>
       <c r="T84">
-        <v>5.573420645108897</v>
+        <v>5.901268918350597</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.09085351954637462</v>
+        <v>0.08975889882894844</v>
       </c>
       <c r="W84">
-        <v>0.182556613275088</v>
+        <v>0.1827764131151472</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5344324679198507</v>
+        <v>0.5279935225232261</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2029296633935509</v>
+        <v>0.2044796633935509</v>
       </c>
       <c r="C85">
-        <v>-200.6309296019393</v>
+        <v>-207.3800255255608</v>
       </c>
       <c r="D85">
-        <v>158.5490703980607</v>
+        <v>157.1599744744393</v>
       </c>
       <c r="E85">
-        <v>211.8800000000001</v>
+        <v>217.2400000000001</v>
       </c>
       <c r="F85">
-        <v>444.8800000000001</v>
+        <v>450.2400000000001</v>
       </c>
       <c r="G85">
         <v>85.7</v>
@@ -8251,37 +8251,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M85">
-        <v>89.33190400000001</v>
+        <v>90.40819200000001</v>
       </c>
       <c r="N85">
-        <v>-42.16523733333334</v>
+        <v>-43.24152533333334</v>
       </c>
       <c r="O85">
-        <v>-7.168090346666668</v>
+        <v>-7.351059306666669</v>
       </c>
       <c r="P85">
-        <v>-34.99714698666667</v>
+        <v>-35.89046602666667</v>
       </c>
       <c r="Q85">
-        <v>-23.89714698666667</v>
+        <v>-24.79046602666667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3013249441645808</v>
+        <v>0.3172952531748672</v>
       </c>
       <c r="T85">
-        <v>5.901268918350597</v>
+        <v>6.270098225747511</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.08975889882894844</v>
+        <v>0.08869034050955618</v>
       </c>
       <c r="W85">
-        <v>0.1827764131151472</v>
+        <v>0.1829909796256811</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5279935225232261</v>
+        <v>0.5217078853503305</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2044796633935509</v>
+        <v>0.2060296633935509</v>
       </c>
       <c r="C86">
-        <v>-207.3800255255607</v>
+        <v>-214.104992280649</v>
       </c>
       <c r="D86">
-        <v>157.1599744744393</v>
+        <v>155.7950077193509</v>
       </c>
       <c r="E86">
-        <v>217.24</v>
+        <v>222.6</v>
       </c>
       <c r="F86">
-        <v>450.24</v>
+        <v>455.6</v>
       </c>
       <c r="G86">
         <v>85.7</v>
@@ -8333,37 +8333,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M86">
-        <v>90.408192</v>
+        <v>91.48447999999999</v>
       </c>
       <c r="N86">
-        <v>-43.24152533333333</v>
+        <v>-44.31781333333332</v>
       </c>
       <c r="O86">
-        <v>-7.351059306666667</v>
+        <v>-7.534028266666665</v>
       </c>
       <c r="P86">
-        <v>-35.89046602666666</v>
+        <v>-36.78378506666665</v>
       </c>
       <c r="Q86">
-        <v>-24.79046602666666</v>
+        <v>-25.68378506666665</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.317295253174867</v>
+        <v>0.3353949367198581</v>
       </c>
       <c r="T86">
-        <v>6.270098225747506</v>
+        <v>6.688104774130673</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.0886903405095562</v>
+        <v>0.08764692473885555</v>
       </c>
       <c r="W86">
-        <v>0.1829909796256811</v>
+        <v>0.1832004975124378</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5217078853503305</v>
+        <v>0.5155701455226797</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2060296633935509</v>
+        <v>0.2075796633935509</v>
       </c>
       <c r="C87">
-        <v>-214.104992280649</v>
+        <v>-220.806453154227</v>
       </c>
       <c r="D87">
-        <v>155.7950077193509</v>
+        <v>154.453546845773</v>
       </c>
       <c r="E87">
-        <v>222.6</v>
+        <v>227.96</v>
       </c>
       <c r="F87">
-        <v>455.6</v>
+        <v>460.96</v>
       </c>
       <c r="G87">
         <v>85.7</v>
@@ -8415,37 +8415,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M87">
-        <v>91.48447999999999</v>
+        <v>92.560768</v>
       </c>
       <c r="N87">
-        <v>-44.31781333333332</v>
+        <v>-45.39410133333332</v>
       </c>
       <c r="O87">
-        <v>-7.534028266666665</v>
+        <v>-7.716997226666666</v>
       </c>
       <c r="P87">
-        <v>-36.78378506666665</v>
+        <v>-37.67710410666666</v>
       </c>
       <c r="Q87">
-        <v>-25.68378506666665</v>
+        <v>-26.57710410666666</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3353949367198581</v>
+        <v>0.3560802893427051</v>
       </c>
       <c r="T87">
-        <v>6.688104774130673</v>
+        <v>7.165826543711437</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08764692473885555</v>
+        <v>0.08662777445119443</v>
       </c>
       <c r="W87">
-        <v>0.1832004975124378</v>
+        <v>0.1834051428902002</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5155701455226797</v>
+        <v>0.5095751438305555</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2075796633935509</v>
+        <v>0.2091296633935509</v>
       </c>
       <c r="C88">
-        <v>-220.806453154227</v>
+        <v>-227.4850101495205</v>
       </c>
       <c r="D88">
-        <v>154.453546845773</v>
+        <v>153.1349898504795</v>
       </c>
       <c r="E88">
-        <v>227.96</v>
+        <v>233.32</v>
       </c>
       <c r="F88">
-        <v>460.96</v>
+        <v>466.32</v>
       </c>
       <c r="G88">
         <v>85.7</v>
@@ -8497,37 +8497,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M88">
-        <v>92.560768</v>
+        <v>93.637056</v>
       </c>
       <c r="N88">
-        <v>-45.39410133333332</v>
+        <v>-46.47038933333333</v>
       </c>
       <c r="O88">
-        <v>-7.716997226666666</v>
+        <v>-7.899966186666667</v>
       </c>
       <c r="P88">
-        <v>-37.67710410666666</v>
+        <v>-38.57042314666666</v>
       </c>
       <c r="Q88">
-        <v>-26.57710410666666</v>
+        <v>-27.47042314666666</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3560802893427051</v>
+        <v>0.3799480039075286</v>
       </c>
       <c r="T88">
-        <v>7.165826543711437</v>
+        <v>7.717043970150778</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08662777445119443</v>
+        <v>0.0856320529057784</v>
       </c>
       <c r="W88">
-        <v>0.1834051428902002</v>
+        <v>0.1836050837765197</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5095751438305555</v>
+        <v>0.5037179582692847</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2091296633935509</v>
+        <v>0.2419986851927209</v>
       </c>
       <c r="C89">
-        <v>-227.4850101495205</v>
+        <v>-256.3180186613413</v>
       </c>
       <c r="D89">
-        <v>153.1349898504795</v>
+        <v>129.6619813386587</v>
       </c>
       <c r="E89">
-        <v>233.32</v>
+        <v>238.68</v>
       </c>
       <c r="F89">
-        <v>466.32</v>
+        <v>471.68</v>
       </c>
       <c r="G89">
         <v>85.7</v>
@@ -8579,45 +8579,45 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M89">
-        <v>93.637056</v>
+        <v>111.222144</v>
       </c>
       <c r="N89">
-        <v>-46.47038933333333</v>
+        <v>-64.05547733333333</v>
       </c>
       <c r="O89">
-        <v>-7.899966186666667</v>
+        <v>-10.88943114666667</v>
       </c>
       <c r="P89">
-        <v>-38.57042314666666</v>
+        <v>-53.16604618666666</v>
       </c>
       <c r="Q89">
-        <v>-27.47042314666666</v>
+        <v>-42.06604618666666</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3799480039075286</v>
+        <v>0.4121188525595731</v>
       </c>
       <c r="T89">
-        <v>7.717043970150778</v>
+        <v>8.460019689597534</v>
       </c>
       <c r="U89">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0856320529057784</v>
+        <v>0.07209295779564666</v>
       </c>
       <c r="W89">
-        <v>0.1836050837765197</v>
+        <v>0.2188004805517865</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5037179582692847</v>
+        <v>0.4240762223273332</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2419986851927209</v>
+        <v>0.2438986851927209</v>
       </c>
       <c r="C90">
-        <v>-256.3180186613413</v>
+        <v>-262.8168060615937</v>
       </c>
       <c r="D90">
-        <v>129.6619813386587</v>
+        <v>128.5231939384063</v>
       </c>
       <c r="E90">
-        <v>238.68</v>
+        <v>244.04</v>
       </c>
       <c r="F90">
-        <v>471.68</v>
+        <v>477.04</v>
       </c>
       <c r="G90">
         <v>85.7</v>
@@ -8661,37 +8661,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M90">
-        <v>111.222144</v>
+        <v>112.486032</v>
       </c>
       <c r="N90">
-        <v>-64.05547733333333</v>
+        <v>-65.31936533333334</v>
       </c>
       <c r="O90">
-        <v>-10.88943114666667</v>
+        <v>-11.10429210666667</v>
       </c>
       <c r="P90">
-        <v>-53.16604618666666</v>
+        <v>-54.21507322666667</v>
       </c>
       <c r="Q90">
-        <v>-42.06604618666666</v>
+        <v>-43.11507322666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4121188525595731</v>
+        <v>0.4454205664286253</v>
       </c>
       <c r="T90">
-        <v>8.460019689597534</v>
+        <v>9.229112388651856</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07209295779564666</v>
+        <v>0.07128292456198769</v>
       </c>
       <c r="W90">
-        <v>0.2188004805517865</v>
+        <v>0.2189914863882833</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4240762223273332</v>
+        <v>0.4193113209528688</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2438986851927209</v>
+        <v>0.2457986851927209</v>
       </c>
       <c r="C91">
-        <v>-262.8168060615937</v>
+        <v>-269.2957642703898</v>
       </c>
       <c r="D91">
-        <v>128.5231939384063</v>
+        <v>127.4042357296102</v>
       </c>
       <c r="E91">
-        <v>244.04</v>
+        <v>249.4</v>
       </c>
       <c r="F91">
-        <v>477.04</v>
+        <v>482.4</v>
       </c>
       <c r="G91">
         <v>85.7</v>
@@ -8743,37 +8743,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M91">
-        <v>112.486032</v>
+        <v>113.74992</v>
       </c>
       <c r="N91">
-        <v>-65.31936533333334</v>
+        <v>-66.58325333333335</v>
       </c>
       <c r="O91">
-        <v>-11.10429210666667</v>
+        <v>-11.31915306666667</v>
       </c>
       <c r="P91">
-        <v>-54.21507322666667</v>
+        <v>-55.26410026666667</v>
       </c>
       <c r="Q91">
-        <v>-43.11507322666667</v>
+        <v>-44.16410026666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4454205664286253</v>
+        <v>0.4853826230714878</v>
       </c>
       <c r="T91">
-        <v>9.229112388651856</v>
+        <v>10.15202362751704</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07128292456198769</v>
+        <v>0.07049089206685449</v>
       </c>
       <c r="W91">
-        <v>0.2189914863882833</v>
+        <v>0.2191782476506357</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4193113209528688</v>
+        <v>0.4146523062756147</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2457986851927209</v>
+        <v>0.2476986851927209</v>
       </c>
       <c r="C92">
-        <v>-269.2957642703898</v>
+        <v>-275.7554067326898</v>
       </c>
       <c r="D92">
-        <v>127.4042357296102</v>
+        <v>126.3045932673102</v>
       </c>
       <c r="E92">
-        <v>249.4</v>
+        <v>254.76</v>
       </c>
       <c r="F92">
-        <v>482.4</v>
+        <v>487.76</v>
       </c>
       <c r="G92">
         <v>85.7</v>
@@ -8825,37 +8825,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M92">
-        <v>113.74992</v>
+        <v>115.013808</v>
       </c>
       <c r="N92">
-        <v>-66.58325333333335</v>
+        <v>-67.84714133333333</v>
       </c>
       <c r="O92">
-        <v>-11.31915306666667</v>
+        <v>-11.53401402666667</v>
       </c>
       <c r="P92">
-        <v>-55.26410026666667</v>
+        <v>-56.31312730666666</v>
       </c>
       <c r="Q92">
-        <v>-44.16410026666667</v>
+        <v>-45.21312730666666</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4853826230714878</v>
+        <v>0.5342251367460975</v>
       </c>
       <c r="T92">
-        <v>10.15202362751704</v>
+        <v>11.28002625279671</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07049089206685449</v>
+        <v>0.06971626687930665</v>
       </c>
       <c r="W92">
-        <v>0.2191782476506357</v>
+        <v>0.2193609042698595</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4146523062756147</v>
+        <v>0.4100956875253332</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2476986851927209</v>
+        <v>0.2495986851927209</v>
       </c>
       <c r="C93">
-        <v>-275.7554067326898</v>
+        <v>-282.1962293187045</v>
       </c>
       <c r="D93">
-        <v>126.3045932673102</v>
+        <v>125.2237706812955</v>
       </c>
       <c r="E93">
-        <v>254.76</v>
+        <v>260.12</v>
       </c>
       <c r="F93">
-        <v>487.76</v>
+        <v>493.12</v>
       </c>
       <c r="G93">
         <v>85.7</v>
@@ -8907,37 +8907,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M93">
-        <v>115.013808</v>
+        <v>116.277696</v>
       </c>
       <c r="N93">
-        <v>-67.84714133333333</v>
+        <v>-69.11102933333333</v>
       </c>
       <c r="O93">
-        <v>-11.53401402666667</v>
+        <v>-11.74887498666667</v>
       </c>
       <c r="P93">
-        <v>-56.31312730666666</v>
+        <v>-57.36215434666667</v>
       </c>
       <c r="Q93">
-        <v>-45.21312730666666</v>
+        <v>-46.26215434666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5342251367460975</v>
+        <v>0.5952782788393599</v>
       </c>
       <c r="T93">
-        <v>11.28002625279671</v>
+        <v>12.69002953439631</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06971626687930665</v>
+        <v>0.06895848136974897</v>
       </c>
       <c r="W93">
-        <v>0.2193609042698595</v>
+        <v>0.2195395900930132</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4100956875253332</v>
+        <v>0.4056381257044057</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2495986851927209</v>
+        <v>0.2514986851927209</v>
       </c>
       <c r="C94">
-        <v>-282.1962293187045</v>
+        <v>-288.6187110694734</v>
       </c>
       <c r="D94">
-        <v>125.2237706812955</v>
+        <v>124.1612889305267</v>
       </c>
       <c r="E94">
-        <v>260.12</v>
+        <v>265.48</v>
       </c>
       <c r="F94">
-        <v>493.12</v>
+        <v>498.48</v>
       </c>
       <c r="G94">
         <v>85.7</v>
@@ -8989,37 +8989,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M94">
-        <v>116.277696</v>
+        <v>117.541584</v>
       </c>
       <c r="N94">
-        <v>-69.11102933333333</v>
+        <v>-70.37491733333334</v>
       </c>
       <c r="O94">
-        <v>-11.74887498666667</v>
+        <v>-11.96373594666667</v>
       </c>
       <c r="P94">
-        <v>-57.36215434666667</v>
+        <v>-58.41118138666668</v>
       </c>
       <c r="Q94">
-        <v>-46.26215434666667</v>
+        <v>-47.31118138666668</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5952782788393599</v>
+        <v>0.6737751758164114</v>
       </c>
       <c r="T94">
-        <v>12.69002953439631</v>
+        <v>14.50289089645292</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06895848136974897</v>
+        <v>0.06821699232276242</v>
       </c>
       <c r="W94">
-        <v>0.2195395900930132</v>
+        <v>0.2197144332102926</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4056381257044057</v>
+        <v>0.4012764254280142</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2514986851927209</v>
+        <v>0.253398685192721</v>
       </c>
       <c r="C95">
-        <v>-288.6187110694734</v>
+        <v>-295.0233149048084</v>
       </c>
       <c r="D95">
-        <v>124.1612889305267</v>
+        <v>123.1166850951916</v>
       </c>
       <c r="E95">
-        <v>265.48</v>
+        <v>270.84</v>
       </c>
       <c r="F95">
-        <v>498.48</v>
+        <v>503.84</v>
       </c>
       <c r="G95">
         <v>85.7</v>
@@ -9071,37 +9071,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M95">
-        <v>117.541584</v>
+        <v>118.805472</v>
       </c>
       <c r="N95">
-        <v>-70.37491733333334</v>
+        <v>-71.63880533333334</v>
       </c>
       <c r="O95">
-        <v>-11.96373594666667</v>
+        <v>-12.17859690666667</v>
       </c>
       <c r="P95">
-        <v>-58.41118138666668</v>
+        <v>-59.46020842666667</v>
       </c>
       <c r="Q95">
-        <v>-47.31118138666668</v>
+        <v>-48.36020842666667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6737751758164114</v>
+        <v>0.7784377051191468</v>
       </c>
       <c r="T95">
-        <v>14.50289089645292</v>
+        <v>16.92003937919508</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06821699232276242</v>
+        <v>0.06749127963847772</v>
       </c>
       <c r="W95">
-        <v>0.2197144332102926</v>
+        <v>0.219885556261247</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4012764254280142</v>
+        <v>0.397007527285163</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.253398685192721</v>
+        <v>0.2552986851927209</v>
       </c>
       <c r="C96">
-        <v>-295.0233149048084</v>
+        <v>-301.4104882957978</v>
       </c>
       <c r="D96">
-        <v>123.1166850951916</v>
+        <v>122.0895117042022</v>
       </c>
       <c r="E96">
-        <v>270.84</v>
+        <v>276.2</v>
       </c>
       <c r="F96">
-        <v>503.84</v>
+        <v>509.2</v>
       </c>
       <c r="G96">
         <v>85.7</v>
@@ -9153,37 +9153,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M96">
-        <v>118.805472</v>
+        <v>120.06936</v>
       </c>
       <c r="N96">
-        <v>-71.63880533333334</v>
+        <v>-72.90269333333335</v>
       </c>
       <c r="O96">
-        <v>-12.17859690666667</v>
+        <v>-12.39345786666667</v>
       </c>
       <c r="P96">
-        <v>-59.46020842666667</v>
+        <v>-60.50923546666667</v>
       </c>
       <c r="Q96">
-        <v>-48.36020842666667</v>
+        <v>-49.40923546666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7784377051191468</v>
+        <v>0.9249652461429766</v>
       </c>
       <c r="T96">
-        <v>16.92003937919508</v>
+        <v>20.30404725503411</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06749127963847772</v>
+        <v>0.06678084511596742</v>
       </c>
       <c r="W96">
-        <v>0.219885556261247</v>
+        <v>0.2200530767216549</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.397007527285163</v>
+        <v>0.3928285006821612</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2552986851927209</v>
+        <v>0.2571986851927209</v>
       </c>
       <c r="C97">
-        <v>-301.4104882957978</v>
+        <v>-307.7806639039243</v>
       </c>
       <c r="D97">
-        <v>122.0895117042022</v>
+        <v>121.0793360960757</v>
       </c>
       <c r="E97">
-        <v>276.2</v>
+        <v>281.5600000000001</v>
       </c>
       <c r="F97">
-        <v>509.2</v>
+        <v>514.5600000000001</v>
       </c>
       <c r="G97">
         <v>85.7</v>
@@ -9235,37 +9235,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M97">
-        <v>120.06936</v>
+        <v>121.333248</v>
       </c>
       <c r="N97">
-        <v>-72.90269333333335</v>
+        <v>-74.16658133333335</v>
       </c>
       <c r="O97">
-        <v>-12.39345786666667</v>
+        <v>-12.60831882666667</v>
       </c>
       <c r="P97">
-        <v>-60.50923546666667</v>
+        <v>-61.55826250666668</v>
       </c>
       <c r="Q97">
-        <v>-49.40923546666667</v>
+        <v>-50.45826250666668</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9249652461429766</v>
+        <v>1.144756557678721</v>
       </c>
       <c r="T97">
-        <v>20.30404725503411</v>
+        <v>25.38005906879264</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06678084511596742</v>
+        <v>0.06608521131267608</v>
       </c>
       <c r="W97">
-        <v>0.2200530767216549</v>
+        <v>0.220217107172471</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3928285006821612</v>
+        <v>0.3887365371333887</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2571986851927209</v>
+        <v>0.2590986851927209</v>
       </c>
       <c r="C98">
-        <v>-307.7806639039242</v>
+        <v>-314.1342601887147</v>
       </c>
       <c r="D98">
-        <v>121.0793360960757</v>
+        <v>120.0857398112852</v>
       </c>
       <c r="E98">
-        <v>281.5599999999999</v>
+        <v>286.92</v>
       </c>
       <c r="F98">
-        <v>514.5599999999999</v>
+        <v>519.92</v>
       </c>
       <c r="G98">
         <v>85.7</v>
@@ -9317,37 +9317,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M98">
-        <v>121.333248</v>
+        <v>122.597136</v>
       </c>
       <c r="N98">
-        <v>-74.16658133333333</v>
+        <v>-75.43046933333332</v>
       </c>
       <c r="O98">
-        <v>-12.60831882666667</v>
+        <v>-12.82317978666667</v>
       </c>
       <c r="P98">
-        <v>-61.55826250666666</v>
+        <v>-62.60728954666666</v>
       </c>
       <c r="Q98">
-        <v>-50.45826250666666</v>
+        <v>-51.50728954666666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.144756557678719</v>
+        <v>1.511075410238291</v>
       </c>
       <c r="T98">
-        <v>25.38005906879258</v>
+        <v>33.84007875839011</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0660852113126761</v>
+        <v>0.06540392047440109</v>
       </c>
       <c r="W98">
-        <v>0.220217107172471</v>
+        <v>0.2203777555521362</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3887365371333888</v>
+        <v>0.3847289439670653</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2590986851927209</v>
+        <v>0.2609986851927209</v>
       </c>
       <c r="C99">
-        <v>-314.1342601887147</v>
+        <v>-320.4716819857152</v>
       </c>
       <c r="D99">
-        <v>120.0857398112852</v>
+        <v>119.1083180142848</v>
       </c>
       <c r="E99">
-        <v>286.92</v>
+        <v>292.28</v>
       </c>
       <c r="F99">
-        <v>519.92</v>
+        <v>525.28</v>
       </c>
       <c r="G99">
         <v>85.7</v>
@@ -9399,37 +9399,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M99">
-        <v>122.597136</v>
+        <v>123.861024</v>
       </c>
       <c r="N99">
-        <v>-75.43046933333332</v>
+        <v>-76.69435733333333</v>
       </c>
       <c r="O99">
-        <v>-12.82317978666667</v>
+        <v>-13.03804074666667</v>
       </c>
       <c r="P99">
-        <v>-62.60728954666666</v>
+        <v>-63.65631658666666</v>
       </c>
       <c r="Q99">
-        <v>-51.50728954666666</v>
+        <v>-52.55631658666666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.511075410238291</v>
+        <v>2.243713115357437</v>
       </c>
       <c r="T99">
-        <v>33.84007875839011</v>
+        <v>50.76011813758515</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06540392047440109</v>
+        <v>0.06473653353078475</v>
       </c>
       <c r="W99">
-        <v>0.2203777555521362</v>
+        <v>0.2205351253934409</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3847289439670653</v>
+        <v>0.3808031384163808</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2609986851927209</v>
+        <v>0.2628986851927209</v>
       </c>
       <c r="C100">
-        <v>-320.4716819857152</v>
+        <v>-326.7933210564667</v>
       </c>
       <c r="D100">
-        <v>119.1083180142848</v>
+        <v>118.1466789435334</v>
       </c>
       <c r="E100">
-        <v>292.28</v>
+        <v>297.64</v>
       </c>
       <c r="F100">
-        <v>525.28</v>
+        <v>530.64</v>
       </c>
       <c r="G100">
         <v>85.7</v>
@@ -9481,37 +9481,37 @@
         <v>47.16666666666667</v>
       </c>
       <c r="M100">
-        <v>123.861024</v>
+        <v>125.124912</v>
       </c>
       <c r="N100">
-        <v>-76.69435733333333</v>
+        <v>-77.95824533333332</v>
       </c>
       <c r="O100">
-        <v>-13.03804074666667</v>
+        <v>-13.25290170666667</v>
       </c>
       <c r="P100">
-        <v>-63.65631658666666</v>
+        <v>-64.70534362666666</v>
       </c>
       <c r="Q100">
-        <v>-52.55631658666666</v>
+        <v>-53.60534362666666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.243713115357437</v>
+        <v>4.441626230714873</v>
       </c>
       <c r="T100">
-        <v>50.76011813758515</v>
+        <v>101.5202362751703</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06473653353078475</v>
+        <v>0.06408262915168592</v>
       </c>
       <c r="W100">
-        <v>0.2205351253934409</v>
+        <v>0.2206893160460325</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3808031384163808</v>
+        <v>0.3769566420687407</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2628986851927209</v>
-      </c>
-      <c r="C101">
-        <v>-326.7933210564667</v>
-      </c>
-      <c r="D101">
-        <v>118.1466789435334</v>
-      </c>
-      <c r="E101">
-        <v>297.64</v>
-      </c>
-      <c r="F101">
-        <v>530.64</v>
-      </c>
-      <c r="G101">
-        <v>85.7</v>
-      </c>
-      <c r="H101">
-        <v>303</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>58.26666666666667</v>
-      </c>
-      <c r="K101">
-        <v>11.1</v>
-      </c>
-      <c r="L101">
-        <v>47.16666666666667</v>
-      </c>
-      <c r="M101">
-        <v>125.124912</v>
-      </c>
-      <c r="N101">
-        <v>-77.95824533333332</v>
-      </c>
-      <c r="O101">
-        <v>-13.25290170666667</v>
-      </c>
-      <c r="P101">
-        <v>-64.70534362666666</v>
-      </c>
-      <c r="Q101">
-        <v>-53.60534362666666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.441626230714873</v>
-      </c>
-      <c r="T101">
-        <v>101.5202362751703</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06408262915168592</v>
-      </c>
-      <c r="W101">
-        <v>0.2206893160460325</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3769566420687407</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
